--- a/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
+++ b/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
@@ -11,12 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Структура меню" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мета-теги" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спрос по страницам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шапка сайта" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Структура сайта'!$A$1:$G$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Структура меню'!$A$1:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Мета-теги'!$A$1:$G$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спрос по страницам'!$A$1:$J$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Структура сайта'!$A$1:$G$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Структура меню'!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Мета-теги'!$A$1:$G$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спрос по страницам'!$A$1:$L$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.1" customWidth="1" min="1" max="1"/>
@@ -791,18 +792,18 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Не создавать</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/4-komnatnoy/</t>
+          <t>/remont-kvartir/kuhni/</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ремонт четырёхкомнатной квартиры</t>
+          <t>Ремонт кухни</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -817,13 +818,13 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/kuhni/</t>
+          <t>/remont-kvartir/vannoy/</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ремонт кухни</t>
+          <t>Ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -838,13 +839,13 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/vannoy/</t>
+          <t>/remont-kvartir/sanuzla/</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ремонт ванной комнаты</t>
+          <t>Ремонт санузла</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -859,13 +860,13 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/sanuzla/</t>
+          <t>/remont-kvartir/spalni/</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ремонт санузла</t>
+          <t>Ремонт спальни</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -880,13 +881,13 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/spalni/</t>
+          <t>/remont-kvartir/gostinoy/</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ремонт спальни</t>
+          <t>Ремонт гостиной</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -896,18 +897,18 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/gostinoy/</t>
+          <t>/remont-kvartir/detskoy/</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ремонт гостиной</t>
+          <t>Ремонт детской комнаты</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -922,13 +923,13 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/detskoy/</t>
+          <t>/remont-kvartir/prihozhey/</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Ремонт детской комнаты</t>
+          <t>Ремонт прихожей и коридора</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -943,13 +944,13 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/prihozhey/</t>
+          <t>/remont-kvartir/balkona/</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ремонт прихожей и коридора</t>
+          <t>Ремонт балкона и лоджии</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -964,13 +965,13 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/balkona/</t>
+          <t>/remont-kvartir/tseny/</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Ремонт балкона и лоджии</t>
+          <t>Цены на ремонт квартир</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -985,13 +986,13 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/tseny/</t>
+          <t>/remont-kvartir/v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Цены на ремонт квартир</t>
+          <t>Ремонт в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1006,13 +1007,13 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/v-zhk-shablon/</t>
+          <t>/remont-kvartir/elitnyy/</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Ремонт в ЖК (шаблон)</t>
+          <t>Элитный ремонт квартир</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1022,22 +1023,18 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>/design/</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>/design</t>
-        </is>
-      </c>
+          <t>/remont-kvartir/ekonom/</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера</t>
+          <t>Недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1052,13 +1049,13 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/design/kvartir/</t>
+          <t>/remont-kvartir/hrushchevka/</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера квартиры</t>
+          <t>Ремонт в хрущёвке</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1073,13 +1070,13 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/design/kuhni/</t>
+          <t>/remont-kvartir/stalinka/</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Ремонт в сталинке</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1094,13 +1091,13 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/design/vannoy/</t>
+          <t>/remont-kvartir/panelnyy-dom/</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Ремонт в панельном доме</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1115,13 +1112,13 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/design/spalni/</t>
+          <t>/remont-kvartir/po-stilyu/</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1136,13 +1133,13 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/design/gostinoy/</t>
+          <t>/remont-kvartir/tualeta/</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Ремонт туалета</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1157,13 +1154,13 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/design/detskoy/</t>
+          <t>/remont-kvartir/posle-zaliva/</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Ремонт после залива и пожара</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1178,13 +1175,13 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/design/prihozhey/</t>
+          <t>/remont-kvartir/v-rassrochku/</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Ремонт в рассрочку</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1199,13 +1196,13 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/design/studii/</t>
+          <t>/remont-kvartir/pod-sdachu/</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Ремонт под сдачу в аренду</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1220,13 +1217,13 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/design/ofisov/</t>
+          <t>/remont-kvartir/po-dizayn-proektu/</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Ремонт по дизайн-проекту</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1236,18 +1233,18 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/design/domov/</t>
+          <t>/remont-kvartir/garderobnoy/</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома</t>
+          <t>Ремонт гардеробной</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1262,13 +1259,13 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/design/kommercheskih-pomesheniy/</t>
+          <t>/remont-domov/</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
+          <t>Ремонт домов и коттеджей</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1278,22 +1275,18 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/priemka/</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>/priemka</t>
-        </is>
-      </c>
+          <t>/remont-kommercheskih-pomescheniy/</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Ремонт коммерческих помещений</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1308,13 +1301,13 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/priemka/bez-otdelki/</t>
+          <t>/teplyy-pol/</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Тёплый пол</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1324,18 +1317,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/priemka/s-otdelkoy/</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>/design/</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>/design</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Дизайн интерьера</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1350,13 +1347,13 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/priemka/v-zhk-shablon/</t>
+          <t>/design/kvartir/</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Дизайн интерьера квартиры</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1366,22 +1363,18 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/komplektaciya/</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>/komplekt</t>
-        </is>
-      </c>
+          <t>/design/kuhni/</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Дизайн кухни</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1396,13 +1389,13 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka/</t>
+          <t>/design/vannoy/</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -1417,13 +1410,13 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/design/spalni/</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -1433,18 +1426,18 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/design/gostinoy/</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -1459,13 +1452,13 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazh/</t>
+          <t>/design/detskoy/</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -1480,13 +1473,13 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/design/prihozhey/</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Сантехнические работы</t>
+          <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -1496,18 +1489,18 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/design/studii/</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Дизайн квартиры-студии</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -1522,13 +1515,13 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyaciya/</t>
+          <t>/design/ofisov/</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -1543,13 +1536,13 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty/</t>
+          <t>/design/domov/</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев</t>
+          <t>Дизайн интерьера дома</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -1564,13 +1557,13 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/design/kommercheskih-pomesheniy/</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -1580,18 +1573,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
+          <t>/priemka/</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>/priemka</t>
+        </is>
+      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -1606,13 +1603,13 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/priemka/bez-otdelki/</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -1627,13 +1624,13 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/priemka/s-otdelkoy/</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -1648,13 +1645,13 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/priemka/v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -1664,18 +1661,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Редирект</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/faq/</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
+          <t>/komplektaciya/</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>/komplekt</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -1690,13 +1691,13 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/o-kompanii/</t>
+          <t>/pereplanirovka/</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -1711,13 +1712,13 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/kontakty/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -1727,22 +1728,18 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/partneram/</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>/partners</t>
-        </is>
-      </c>
+          <t>/styazhka-pola/</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -1757,13 +1754,13 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/elektromontazh/</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Электромонтажные работы</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -1773,22 +1770,18 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/politika-konfidencialnosti/</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>/politicakonfident</t>
-        </is>
-      </c>
+          <t>/santehnicheskie-raboty/</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Сантехнические работы</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -1798,22 +1791,18 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/soglasie-na-obrabotku/</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>/soglasienaobrabotku</t>
-        </is>
-      </c>
+          <t>/demontazhnye-raboty/</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -1828,21 +1817,327 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/spasibo/</t>
+          <t>/shumoizolyaciya/</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Спасибо за заявку</t>
+          <t>Шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>/malyarnye-raboty/</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и поклейка обоев</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>/ukladka-plitki/</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>/natyazhnye-potolki/</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>/vyravnivanie-sten/</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>/faq/</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>/o-kompanii/</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>О компании</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>/kontakty/</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Редирект</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>/partneram/</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>/partners</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>/blog/</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Блог</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Редирект</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>/politika-konfidencialnosti/</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>/politicakonfident</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Редирект</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>/soglasie-na-obrabotku/</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>/soglasienaobrabotku</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>/spasibo/</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за заявку</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G64"/>
+  <autoFilter ref="A1:G78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1853,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.8" customWidth="1" min="1" max="1"/>
@@ -1863,6 +2158,11 @@
     <col width="25.8" customWidth="1" min="5" max="5"/>
     <col width="25.8" customWidth="1" min="6" max="6"/>
     <col width="25.8" customWidth="1" min="7" max="7"/>
+    <col width="25.8" customWidth="1" min="8" max="8"/>
+    <col width="25.8" customWidth="1" min="9" max="9"/>
+    <col width="25.8" customWidth="1" min="10" max="10"/>
+    <col width="25.8" customWidth="1" min="11" max="11"/>
+    <col width="25.8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1878,34 +2178,59 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Приёмка</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Услуги</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Портфолио</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Блог</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>О компании</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Блог</t>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Контакты</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартиры в новостройке</t>
+          <t>По виду ремонта</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1913,28 +2238,29 @@
           <t>Дизайн интерьера квартиры</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Комплектация квартиры</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Отзывы</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Перепланировка квартиры</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартиры на вторичке</t>
+          <t xml:space="preserve">  Ремонт квартиры в новостройке</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1942,28 +2268,29 @@
           <t>Дизайн кухни</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Перепланировка квартиры</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Вопросы и ответы</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Механизированная штукатурка</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Капитальный ремонт квартиры</t>
+          <t xml:space="preserve">  Ремонт квартиры на вторичке</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1971,28 +2298,29 @@
           <t>Дизайн ванной комнаты</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Механизированная штукатурка</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Партнёрам</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Стяжка пола</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Косметический ремонт квартиры</t>
+          <t xml:space="preserve">  Капитальный ремонт квартиры</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2001,23 +2329,24 @@
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Стяжка пола</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Контакты</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Дизайнерский ремонт квартиры</t>
+          <t xml:space="preserve">  Косметический ремонт квартиры</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2026,19 +2355,24 @@
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Выравнивание стен</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и поклейка обоев</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Черновой ремонт квартиры</t>
+          <t xml:space="preserve">  Дизайнерский ремонт квартиры</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2047,19 +2381,24 @@
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Малярные работы и поклейка обоев</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Чистовая отделка квартиры</t>
+          <t xml:space="preserve">  Ремонт по дизайн-проекту</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2068,19 +2407,24 @@
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Укладка плитки</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Электромонтажные работы</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Евроремонт квартиры</t>
+          <t xml:space="preserve">  Черновой ремонт квартиры</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2089,19 +2433,24 @@
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Электромонтажные работы</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Сантехнические работы</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартиры-студии</t>
+          <t xml:space="preserve">  Чистовая отделка квартиры</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2110,19 +2459,24 @@
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Демонтажные работы</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Тёплый пол</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Ремонт однокомнатной квартиры</t>
+          <t xml:space="preserve">  Евроремонт квартиры</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2131,19 +2485,24 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Шумоизоляция квартиры</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Демонтажные работы</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Ремонт двухкомнатной квартиры</t>
+          <t xml:space="preserve">  Элитный ремонт квартир</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2152,32 +2511,46 @@
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Натяжные потолки</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция квартиры</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Ремонт трёхкомнатной квартиры</t>
+          <t xml:space="preserve">  Недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Ремонт кухни</t>
+          <t xml:space="preserve">  Ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
@@ -2186,11 +2559,16 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Ремонт ванной комнаты</t>
+          <t xml:space="preserve">  Ремонт после залива и пожара</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
@@ -2199,11 +2577,16 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Ремонт санузла</t>
+          <t xml:space="preserve">  Ремонт в рассрочку</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
@@ -2212,11 +2595,16 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Ремонт спальни</t>
+          <t xml:space="preserve">  Ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -2225,11 +2613,16 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Ремонт гостиной</t>
+          <t>По числу комнат</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -2238,11 +2631,16 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ремонт детской комнаты</t>
+          <t xml:space="preserve">  Ремонт квартиры-студии</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
@@ -2251,11 +2649,16 @@
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Ремонт прихожей и коридора</t>
+          <t xml:space="preserve">  Ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
@@ -2264,11 +2667,16 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Ремонт балкона и лоджии</t>
+          <t xml:space="preserve">  Ремонт двухкомнатной квартиры</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
@@ -2277,11 +2685,16 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Цены на ремонт квартир</t>
+          <t xml:space="preserve">  Ремонт трёхкомнатной квартиры</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -2290,11 +2703,16 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Ремонт в ЖК (шаблон)</t>
+          <t>По типу дома</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
@@ -2303,9 +2721,356 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт в хрущёвке</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт в сталинке</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт в панельном доме</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт кухни</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт ванной комнаты</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт санузла</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт туалета</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт спальни</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт гостиной</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт детской комнаты</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт прихожей и коридора</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт балкона и лоджии</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт гардеробной</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Цены на ремонт квартир</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт в ЖК (шаблон)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт домов и коттеджей</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ремонт коммерческих помещений</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:L42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2316,7 +3081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.5" customWidth="1" min="1" max="1"/>
@@ -3112,136 +3877,136 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера</t>
+          <t>Элитный ремонт квартир</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера в Москве, цена за м² | СК Эспада</t>
+          <t>Элитный ремонт квартир в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Разрабатываем дизайн-проекты квартир, домов и офисов от 1 790 ₽ за м². Технический и стандартный тариф, авторский надзор. Выезд дизайнера на объект бесплатный.</t>
+          <t>Элитный ремонт квартиры премиум-класса: авторский надзор дизайнера, материалы верхнего сегмента, скрытые инженерные решения. Ведём объект от демонтажа до мебели.</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера в Москве</t>
+          <t>Элитный ремонт квартир</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера квартиры</t>
+          <t>Недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Дизайн-проект квартиры в Москве от 1 790 ₽ за м² | СК Эспада</t>
+          <t>Недорогой ремонт квартир в Москве от 7 200 ₽/м² | СК Эспада</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Дизайн-проект квартиры: обмеры, планировочные решения, схемы электрики и сантехники, развёртки, ведомости отделки. Проект проверяем на выполнимость до сметы.</t>
+          <t>Недорогой ремонт квартиры без потери качества: считаем смету по фактическим объёмам, подбираем материалы под бюджет, платите по этапам. Расчёт бесплатный.</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Дизайн-проект квартиры</t>
+          <t>Недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Ремонт в хрущёвке</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни в Москве, разработка проекта | СК Эспада</t>
+          <t>Ремонт квартиры в хрущёвке под ключ в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни: эргономика рабочего треугольника, расстановка техники, схемы подключения, освещение рабочих зон. Отдаём проект в комплекте с ведомостями.</t>
+          <t>Ремонт в хрущёвке: выравниваем кривые стены, меняем проводку и трубы, работаем с низкими потолками и маленькими кухнями. Перепланировку согласуем до старта работ.</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Ремонт квартиры в хрущёвке</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Ремонт в сталинке</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты в Москве под ключ | СК Эспада</t>
+          <t>Ремонт квартиры в сталинке под ключ в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты: раскладка плитки, развёртки стен, схемы подключения сантехники, освещение и вентиляция. Учитываем размеры помещения и вкус хозяев.</t>
+          <t>Ремонт в сталинке: работаем с высокими потолками, деревянными перекрытиями и старой проводкой. Учитываем ограничения дома и требования по охране фасада.</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Ремонт квартиры в сталинке</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Ремонт в панельном доме</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни в Москве, проект интерьера | СК Эспада</t>
+          <t>Ремонт квартиры в панельном доме в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3249,38 +4014,38 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни: планировка, сценарии освещения, системы хранения, подбор отделки и текстиля. Отдаём проект со всеми схемами и ведомостью материалов.</t>
+          <t>Ремонт в панельном доме: заделываем межпанельные швы, выравниваем плиты, усиливаем шумоизоляцию. Несущие панели не трогаем, перепланировку согласуем.</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Ремонт квартиры в панельном доме</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной в Москве, проект интерьера | СК Эспада</t>
+          <t>Ремонт квартиры в стиле лофт, сканди и неоклассика | СК Эспада</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной: зонирование, расстановка мебели, освещение, отделка стен и потолка. Готовим проект, по которому объект собирают без переделок на площадке.</t>
+          <t>Ремонт под конкретный стиль интерьера: лофт, сканди, минимализм, неоклассика. Подбираем материалы и решения под выбранное направление, работаем по проекту.</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
@@ -3288,216 +4053,216 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Ремонт туалета</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты в Москве под ключ | СК Эспада</t>
+          <t>Ремонт туалета под ключ в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты: безопасные материалы, зоны сна, игры и учёбы, освещение по нормам. Закладываем запас на взросление ребёнка. Выезд дизайнера бесплатный.</t>
+          <t>Ремонт туалета под ключ: демонтаж, гидроизоляция, разводка труб, укладка плитки, установка унитаза и инсталляции. Работаем с раздельными санузлами любой площади.</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Ремонт туалета</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Ремонт после залива и пожара</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора в Москве | СК Эспада</t>
+          <t>Ремонт квартиры после залива и пожара в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора: системы хранения, износостойкая отделка, освещение узких пространств. Проект с развёртками и ведомостью отделочных материалов.</t>
+          <t>Восстановительный ремонт после залива или пожара: оцениваем ущерб, просушиваем конструкции, устраняем запах, восстанавливаем отделку. Готовим документы для страховой.</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Ремонт после залива и пожара</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Ремонт в рассрочку</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии в Москве, проект | СК Эспада</t>
+          <t>Ремонт квартиры в рассрочку в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Дизайн студии: зонирование без стен, компактные системы хранения, продуманное освещение. Работаем с площадями от 18 м². Отдаём полный комплект чертежей.</t>
+          <t>Ремонт квартиры в рассрочку: платите по мере выполнения этапов, без переплаты и банка. Смета фиксируется договором и не меняется после подписания.</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Ремонт квартиры в рассрочку</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Ремонт под сдачу в аренду</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса в Москве, проект | СК Эспада</t>
+          <t>Ремонт квартиры под сдачу в аренду в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Дизайн офиса: планировка рабочих мест, переговорные и зоны отдыха, освещение и акустика по нормам. Готовим проект под согласование с собственником здания.</t>
+          <t>Ремонт под сдачу: износостойкая отделка, простая в уходе, короткие сроки и понятный бюджет. Считаем смету так, чтобы вложения окупились арендой.</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома</t>
+          <t>Ремонт по дизайн-проекту</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома и коттеджа в Москве | СК Эспада</t>
+          <t>Ремонт квартиры по дизайн-проекту в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера частного дома: планировка по этажам, лестницы, инженерные решения, отделка. Ведём проект от обмеров до авторского надзора на объекте.</t>
+          <t>Ремонт по готовому дизайн-проекту, в том числе чужому. Проверяем проект на ошибки до сметы: находим то, что нельзя реализовать, и предлагаем замену.</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома</t>
+          <t>Ремонт по дизайн-проекту</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
+          <t>Ремонт гардеробной</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений в Москве | СК Эспада</t>
+          <t>Ремонт и отделка гардеробной в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений: магазины, салоны, кафе и офисы. Учитываем сценарии посетителей, нормы и требования арендодателя. Проект с полным комплектом схем.</t>
+          <t>Отделка гардеробной комнаты: освещение, вентиляция, подготовка стен под системы хранения. Считаем по фактической площади, работаем по договору.</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
+          <t>Ремонт гардеробной</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Ремонт домов и коттеджей</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в новостройке в Москве | СК Эспада</t>
+          <t>Ремонт домов и коттеджей в Москве и области | СК Эспада</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры от застройщика с инженером: находим скрытые дефекты и составляем акт с замечаниями. Проверяем конструкции, отделку, окна и инженерные системы.</t>
+          <t>Ремонт частного дома, коттеджа или таунхауса под ключ: внутренняя отделка, инженерные системы, работа по этажам. Смета фиксируется договором, оплата по этапам.</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
@@ -3505,30 +4270,30 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в новостройке</t>
+          <t>Ремонт домов и коттеджей</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Ремонт коммерческих помещений</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки в Москве | СК Эспада</t>
+          <t>Ремонт коммерческих помещений в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки: проверяем геометрию стен, стяжку, окна, вентиляцию и вводы коммуникаций. Отдаём акт с замечаниями для передачи застройщику.</t>
+          <t>Ремонт офисов, магазинов, салонов и кафе: работаем по проекту и требованиям арендодателя, укладываемся в согласованные окна работ. Сдаём с документацией.</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
@@ -3536,216 +4301,216 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Ремонт коммерческих помещений</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Тёплый пол</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой от застройщика | СК Эспада</t>
+          <t>Монтаж тёплого пола в квартире в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с чистовой отделкой: проверяем качество работ, сантехнику, электрику, двери и окна. Фиксируем дефекты в акте и помогаем добиться устранения.</t>
+          <t>Монтаж тёплого пола, водяного и электрического: расчёт мощности, укладка контура, подключение и настройка терморегулятора. Считаем по фактической площади.</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Монтаж тёплого пола</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Дизайн интерьера</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название} | СК Эспада</t>
+          <t>Дизайн интерьера в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название}: знаем типовые дефекты этого дома и порядок работы с застройщиком. Выезд инженера с инструментом, акт в день осмотра.</t>
+          <t>Разрабатываем дизайн-проекты квартир, домов и офисов от 1 790 ₽ за м². Технический и стандартный тариф, авторский надзор. Выезд дизайнера на объект бесплатный.</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название}</t>
+          <t>Дизайн интерьера в Москве</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Дизайн интерьера квартиры</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры материалами в Москве | СК Эспада</t>
+          <t>Дизайн-проект квартиры в Москве от 1 790 ₽ за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Комплектация ремонта: подбираем черновые и чистовые материалы, мебель и технику. Считаем спецификацию, возим в шоурум, закупаем по ценам поставщиков.</t>
+          <t>Дизайн-проект квартиры: обмеры, планировочные решения, схемы электрики и сантехники, развёртки, ведомости отделки. Проект проверяем на выполнимость до сметы.</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Дизайн-проект квартиры</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Дизайн кухни</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры в Москве, согласование | СК Эспада</t>
+          <t>Дизайн кухни в Москве, разработка проекта | СК Эспада</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры с согласованием: проект, техническое заключение, подача в жилищную инспекцию, ввод изменений в документы. Ведём весь процесс сами.</t>
+          <t>Дизайн кухни: эргономика рабочего треугольника, расстановка техники, схемы подключения, освещение рабочих зон. Отдаём проект в комплекте с ведомостями.</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Дизайн кухни</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен в Москве, цена | СК Эспада</t>
+          <t>Дизайн ванной комнаты в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен по маякам: ровная плоскость под чистовую отделку, скорость выше ручной в разы. Считаем по фактической площади, работаем по договору.</t>
+          <t>Дизайн ванной комнаты: раскладка плитки, развёртки стен, схемы подключения сантехники, освещение и вентиляция. Учитываем размеры помещения и вкус хозяев.</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола в квартире в Москве, цена за м² | СК Эспада</t>
+          <t>Дизайн спальни в Москве, проект интерьера | СК Эспада</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Устройство стяжки пола, полусухой и мокрой, с гидроизоляцией мокрых зон. Выводим горизонт под ламинат и плитку. Считаем по площади, работаем по договору.</t>
+          <t>Дизайн спальни: планировка, сценарии освещения, системы хранения, подбор отделки и текстиля. Отдаём проект со всеми схемами и ведомостью материалов.</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола в квартире</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы в квартире в Москве | СК Эспада</t>
+          <t>Дизайн гостиной в Москве, проект интерьера | СК Эспада</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Электромонтаж в квартире: разводка сетей, установка щита и электроточек, замена проводки. Работаем по схеме из проекта, сдаём этап с исполнительной схемой.</t>
+          <t>Дизайн гостиной: зонирование, расстановка мебели, освещение, отделка стен и потолка. Готовим проект, по которому объект собирают без переделок на площадке.</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
@@ -3753,247 +4518,247 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы в квартире</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы в квартире в Москве, цены | СК Эспада</t>
+          <t>Дизайн детской комнаты в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж в квартире: снос перегородок по согласованию, снятие старой отделки и стяжки, вывоз мусора. Работаем с допуском от управляющей компании.</t>
+          <t>Дизайн детской комнаты: безопасные материалы, зоны сна, игры и учёбы, освещение по нормам. Закладываем запас на взросление ребёнка. Выезд дизайнера бесплатный.</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы в квартире</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры в Москве под ключ | СК Эспада</t>
+          <t>Дизайн прихожей и коридора в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры: стены, потолок, пол и входная дверь. Подбираем конструкцию под источник шума и считаем потерю площади заранее. Замер бесплатный.</t>
+          <t>Дизайн прихожей и коридора: системы хранения, износостойкая отделка, освещение узких пространств. Проект с развёртками и ведомостью отделочных материалов.</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев</t>
+          <t>Дизайн квартиры-студии</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев в Москве, цена | СК Эспада</t>
+          <t>Дизайн квартиры-студии в Москве, проект | СК Эспада</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы: шпатлёвка, покраска стен и потолков, поклейка обоев любых типов. Готовим основание под чистовое покрытие. Считаем по фактической площади.</t>
+          <t>Дизайн студии: зонирование без стен, компактные системы хранения, продуманное освещение. Работаем с площадями от 18 м². Отдаём полный комплект чертежей.</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев</t>
+          <t>Дизайн квартиры-студии</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки в квартире в Москве, цена за м² | СК Эспада</t>
+          <t>Дизайн интерьера офиса в Москве, проект | СК Эспада</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Укладка керамической плитки и керамогранита: подготовка основания, гидроизоляция, раскладка по проекту, затирка швов. Считаем по фактической площади.</t>
+          <t>Дизайн офиса: планировка рабочих мест, переговорные и зоны отдыха, освещение и акустика по нормам. Готовим проект под согласование с собственником здания.</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Дизайн интерьера дома</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки в Москве под ключ, цена | СК Эспада</t>
+          <t>Дизайн интерьера дома и коттеджа в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки, матовые, сатиновые и глянцевые, с монтажом светильников и коробов. Ставим в рамках комплексного ремонта или отдельной работой.</t>
+          <t>Дизайн интерьера частного дома: планировка по этажам, лестницы, инженерные решения, отделка. Ведём проект от обмеров до авторского надзора на объекте.</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Дизайн интерьера дома</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен в квартире в Москве, цена | СК Эспада</t>
+          <t>Дизайн коммерческих помещений в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен под чистовую отделку: штукатурка по маякам, шпатлёвка, контроль плоскости правилом. Считаем по фактической площади, смета в договоре.</t>
+          <t>Дизайн коммерческих помещений: магазины, салоны, кафе и офисы. Учитываем сценарии посетителей, нормы и требования арендодателя. Проект с полным комплектом схем.</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Портфолио ремонтов квартир в Москве, фото работ | СК Эспада</t>
+          <t>Приёмка квартиры в новостройке в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Наши работы: фото готовых квартир, площадь, сроки и состав работ по каждому объекту. Фильтры по типу ремонта, числу комнат и жилому комплексу.</t>
+          <t>Приёмка квартиры от застройщика с инженером: находим скрытые дефекты и составляем акт с замечаниями. Проверяем конструкции, отделку, окна и инженерные системы.</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Портфолио выполненных работ</t>
+          <t>Приёмка квартиры в новостройке</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Отзывы о ремонте квартир от клиентов | СК Эспада</t>
+          <t>Приёмка квартиры без отделки в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Отзывы клиентов о ремонте и дизайне квартир: что заказывали, как шли работы, что получилось. Каждый отзыв можно проверить, к нему приложены фото объекта.</t>
+          <t>Приёмка квартиры без отделки: проверяем геометрию стен, стяжку, окна, вентиляцию и вводы коммуникаций. Отдаём акт с замечаниями для передачи застройщику.</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
@@ -4001,115 +4766,115 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Отзывы клиентов</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы о ремонте квартир | СК Эспада</t>
+          <t>Приёмка квартиры с отделкой от застройщика | СК Эспада</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Отвечаем на вопросы о сроках, смете, договоре, оплате и гарантии. Что входит в ремонт под ключ, как считается стоимость и что делать при изменениях в проекте.</t>
+          <t>Приёмка квартиры с чистовой отделкой: проверяем качество работ, сантехнику, электрику, двери и окна. Фиксируем дефекты в акте и помогаем добиться устранения.</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>О компании СК Эспада, ремонт квартир в Москве</t>
+          <t>Приёмка квартиры в ЖК {Название} | СК Эспада</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>СК «Эспада» делает ремонт и дизайн квартир в Москве и области. Команда, гарантии, лицензии и реквизиты. Работаем по договору с фиксированной сметой.</t>
+          <t>Приёмка квартиры в ЖК {Название}: знаем типовые дефекты этого дома и порядок работы с застройщиком. Выезд инженера с инструментом, акт в день осмотра.</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Приёмка квартиры в ЖК {Название}</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Контакты СК Эспада в Москве, адрес и телефон</t>
+          <t>Комплектация квартиры материалами в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Офис в Москве, улица Дегунинская, дом 1, корпус 2. Телефон +7 (993) 891-40-64, почта sk-espada@rambler.ru. Схема проезда и форма обратной связи.</t>
+          <t>Комплектация ремонта: подбираем черновые и чистовые материалы, мебель и технику. Считаем спецификацию, возим в шоурум, закупаем по ценам поставщиков.</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа для дизайнеров и агентов | СК Эспада</t>
+          <t>Перепланировка квартиры в Москве, согласование | СК Эспада</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -4117,135 +4882,631 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам: стабильный поток клиентов, прозрачные условия и быстрые выплаты. Работаем с дизайнерами, риелторами и смежными подрядчиками. Оставьте заявку.</t>
+          <t>Перепланировка квартиры с согласованием: проект, техническое заключение, подача в жилищную инспекцию, ввод изменений в документы. Ведём весь процесс сами.</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Блог о ремонте и дизайне квартир | СК Эспада</t>
+          <t>Механизированная штукатурка стен в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Статьи о ремонте и дизайне: как считать бюджет, что выбрать из материалов, с чего начинать работы и как контролировать подрядчика. Разборы от инженеров.</t>
+          <t>Механизированная штукатурка стен по маякам: ровная плоскость под чистовую отделку, скорость выше ручной в разы. Считаем по фактической площади, работаем по договору.</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Блог о ремонте и дизайне</t>
+          <t>Механизированная штукатурка стен</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности | СК Эспада</t>
+          <t>Стяжка пола в квартире в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Устройство стяжки пола, полусухой и мокрой, с гидроизоляцией мокрых зон. Выводим горизонт под ламинат и плитку. Считаем по площади, работаем по договору.</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Стяжка пола в квартире</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Электромонтажные работы</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных | СК Эспада</t>
+          <t>Электромонтажные работы в квартире в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Электромонтаж в квартире: разводка сетей, установка щита и электроточек, замена проводки. Работаем по схеме из проекта, сдаём этап с исполнительной схемой.</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Электромонтажные работы в квартире</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>Сантехнические работы</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Сантехнические работы в квартире в Москве, цены | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Сантехника под ключ: замена труб и стояков, разводка водоснабжения и канализации, установка ванны, раковины, унитаза и полотенцесушителя. Сдаём с проверкой на протечки.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Сантехнические работы в квартире</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Демонтажные работы</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Демонтажные работы в квартире в Москве, цены | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж в квартире: снос перегородок по согласованию, снятие старой отделки и стяжки, вывоз мусора. Работаем с допуском от управляющей компании.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Демонтажные работы в квартире</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция квартиры</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция квартиры в Москве под ключ | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция квартиры: стены, потолок, пол и входная дверь. Подбираем конструкцию под источник шума и считаем потерю площади заранее. Замер бесплатный.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция квартиры</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и поклейка обоев</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и поклейка обоев в Москве, цена | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы: шпатлёвка, покраска стен и потолков, поклейка обоев любых типов. Готовим основание под чистовое покрытие. Считаем по фактической площади.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и поклейка обоев</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки в квартире в Москве, цена за м² | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Укладка керамической плитки и керамогранита: подготовка основания, гидроизоляция, раскладка по проекту, затирка швов. Считаем по фактической площади.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки в Москве под ключ, цена | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки, матовые, сатиновые и глянцевые, с монтажом светильников и коробов. Ставим в рамках комплексного ремонта или отдельной работой.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен в квартире в Москве, цена | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен под чистовую отделку: штукатурка по маякам, шпатлёвка, контроль плоскости правилом. Считаем по фактической площади, смета в договоре.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио ремонтов квартир в Москве, фото работ | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Наши работы: фото готовых квартир, площадь, сроки и состав работ по каждому объекту. Фильтры по типу ремонта, числу комнат и жилому комплексу.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио выполненных работ</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы о ремонте квартир от клиентов | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы клиентов о ремонте и дизайне квартир: что заказывали, как шли работы, что получилось. Каждый отзыв можно проверить, к нему приложены фото объекта.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы клиентов</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы о ремонте квартир | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Отвечаем на вопросы о сроках, смете, договоре, оплате и гарантии. Что входит в ремонт под ключ, как считается стоимость и что делать при изменениях в проекте.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>О компании</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>О компании СК Эспада, ремонт квартир в Москве</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>СК «Эспада» делает ремонт и дизайн квартир в Москве и области. Команда, гарантии, лицензии и реквизиты. Работаем по договору с фиксированной сметой.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>О компании</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Контакты СК Эспада в Москве, адрес и телефон</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Офис в Москве, улица Дегунинская, дом 1, корпус 2. Телефон +7 (993) 891-40-64, почта sk-espada@rambler.ru. Схема проезда и форма обратной связи.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрская программа для дизайнеров и агентов | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам: стабильный поток клиентов, прозрачные условия и быстрые выплаты. Работаем с дизайнерами, риелторами и смежными подрядчиками. Оставьте заявку.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Блог</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Блог о ремонте и дизайне квартир | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Статьи о ремонте и дизайне: как считать бюджет, что выбрать из материалов, с чего начинать работы и как контролировать подрядчика. Разборы от инженеров.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Блог о ремонте и дизайне</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
           <t>Спасибо за заявку</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Заявка отправлена | СК Эспада</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C78" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="n">
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Заявка отправлена</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G62"/>
+  <autoFilter ref="A1:G78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4256,7 +5517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4269,6 +5530,8 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4322,6 +5585,16 @@
           <t>Вердикт</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>CTA основной</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>CTA дополнительный</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4345,16 +5618,16 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>80244</v>
+        <v>86424</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>79368</v>
+        <v>86257</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -4364,6 +5637,16 @@
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
@@ -4389,16 +5672,16 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9939</v>
+        <v>7845</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>6521</v>
+        <v>6618</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -4408,6 +5691,16 @@
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -4433,16 +5726,16 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3654</v>
+        <v>3561</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3505</v>
+        <v>3520</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -4452,6 +5745,16 @@
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
@@ -4477,16 +5780,16 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3816</v>
+        <v>3416</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3282</v>
+        <v>3345</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -4496,6 +5799,16 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -4542,6 +5855,12 @@
           <t>Тонко</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4565,16 +5884,16 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2602</v>
+        <v>2455</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2351</v>
+        <v>2426</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -4584,6 +5903,16 @@
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
@@ -4609,16 +5938,16 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2675</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>2683</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>38</v>
-      </c>
       <c r="H8" s="2" t="n">
-        <v>2100</v>
+        <v>2162</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -4630,6 +5959,12 @@
           <t>Ядро полное</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4653,16 +5988,16 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -4672,18 +6007,28 @@
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/balkona/</t>
+          <t>/remont-kvartir/elitnyy/</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Ремонт балкона и лоджии</t>
+          <t>Элитный ремонт квартир</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4697,25 +6042,35 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>812</v>
+        <v>1342</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>802</v>
+        <v>1182</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
@@ -4741,16 +6096,16 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1703</v>
+        <v>1059</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>801</v>
+        <v>847</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -4760,23 +6115,33 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Записаться на приёмку</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Посчитать ремонт после приёмки</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/remont-kvartir/balkona/</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Ремонт балкона и лоджии</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4785,42 +6150,52 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1326</v>
+        <v>820</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>754</v>
+        <v>810</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>укладка плитки цена за м2 в москве и московской</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Ядро полное</t>
+          <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/sanuzla/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Ремонт санузла</t>
+          <t>Укладка плитки</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4829,27 +6204,33 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>617</v>
+        <v>805</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>594</v>
+        <v>793</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>укладка плитки цена за м2 в москве и московской</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Рабочее ядро</t>
-        </is>
-      </c>
+          <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4873,16 +6254,16 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>583</v>
+        <v>521</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -4892,6 +6273,16 @@
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
@@ -4917,10 +6308,10 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>15</v>
@@ -4938,6 +6329,16 @@
           <t>Рабочее ядро</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4961,10 +6362,10 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>542</v>
+        <v>470</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>11</v>
@@ -4982,16 +6383,26 @@
           <t>Рабочее ядро</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/novostroyka/</t>
+          <t>/remont-kvartir/sanuzla/</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартиры в новостройке</t>
+          <t>Ремонт санузла</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5005,37 +6416,47 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>260</v>
+        <v>436</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Ядро полное</t>
+          <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/dizaynerskiy/</t>
+          <t>/remont-kvartir/novostroyka/</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Дизайнерский ремонт квартиры</t>
+          <t>Ремонт квартиры в новостройке</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5049,37 +6470,47 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>245</v>
+        <v>365</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>элитный дизайнерский ремонт квартир в москве</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Тонко</t>
+          <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Принять квартиру и сразу посчитать ремонт</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka/</t>
+          <t>/teplyy-pol/</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Тёплый пол</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5093,20 +6524,20 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>717</v>
+        <v>279</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>перепланировка квартиры в москве согласование под ключ</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5114,21 +6545,27 @@
           <t>Рабочее ядро</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyaciya/</t>
+          <t>/remont-kvartir/dizaynerskiy/</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Дизайнерский ремонт квартиры</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5137,42 +6574,52 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>471</v>
+        <v>272</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит шумоизоляция в квартиру</t>
+          <t>элитный дизайнерский ремонт квартир в москве</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Ядро полное</t>
+          <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/kosmeticheskiy/</t>
+          <t>/shumoizolyaciya/</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Косметический ремонт квартиры</t>
+          <t>Шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5181,37 +6628,43 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>сколько стоит шумоизоляция в квартиру</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Тонко</t>
-        </is>
-      </c>
+          <t>Ядро полное</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/pereplanirovka/</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5225,20 +6678,20 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>229</v>
+        <v>358</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>сухая стяжка пола кнауф</t>
+          <t>перепланировка квартиры в москве согласование под ключ</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5246,21 +6699,27 @@
           <t>Рабочее ядро</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/v-zhk-shablon/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ремонт в ЖК (шаблон)</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5269,42 +6728,48 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>сухая стяжка пола кнауф</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Тонко</t>
-        </is>
-      </c>
+          <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazh/</t>
+          <t>/remont-kvartir/kosmeticheskiy/</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы</t>
+          <t>Косметический ремонт квартиры</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5313,37 +6778,47 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>электромонтаж в квартире</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/elektromontazh/</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Электромонтажные работы</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -5357,37 +6832,43 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>демонтажные работы</t>
+          <t>электромонтаж в квартире</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Тонко</t>
-        </is>
-      </c>
+          <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/2-komnatnoy/</t>
+          <t>/remont-kvartir/v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Ремонт двухкомнатной квартиры</t>
+          <t>Ремонт в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -5401,37 +6882,47 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>70</v>
+        <v>224</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/vtorichka/</t>
+          <t>/remont-kvartir/tualeta/</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартиры на вторичке</t>
+          <t>Ремонт туалета</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5445,37 +6936,47 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Рабочее ядро</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/kapitalnyy/</t>
+          <t>/remont-kvartir/ekonom/</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Капитальный ремонт квартиры</t>
+          <t>Недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5489,42 +6990,52 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Тонко</t>
+          <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>/design/vannoy/</t>
+          <t>/remont-kvartir/kapitalnyy/</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Капитальный ремонт квартиры</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Дизайн</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -5533,37 +7044,47 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>3275</v>
+        <v>96</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект ванной</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Ядро полное</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -5577,42 +7098,48 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>ремонт натяжных потолков после залива цена</t>
+          <t>демонтажные работы</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Рабочее ядро</t>
-        </is>
-      </c>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>/design/ofisov/</t>
+          <t>/remont-kvartir/2-komnatnoy/</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Ремонт двухкомнатной квартиры</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Дизайн</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -5621,42 +7148,52 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект офиса</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Тонко</t>
+          <t>Рабочее ядро</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>/design/kuhni/</t>
+          <t>/remont-kvartir/po-dizayn-proektu/</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Ремонт по дизайн-проекту</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Дизайн</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -5665,42 +7202,52 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1846</v>
+        <v>87</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>арт дизайн кухни</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Ядро полное</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/remont-kvartir/po-stilyu/</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5709,37 +7256,47 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит выравнивание стен</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Рабочее ядро</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/chernovoy/</t>
+          <t>/remont-kvartir/v-rassrochku/</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Черновой ремонт квартиры</t>
+          <t>Ремонт в рассрочку</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5753,42 +7310,52 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт под ключ с материалами цена</t>
+          <t>ремонт в рассрочку</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/3-komnatnoy/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Ремонт трёхкомнатной квартиры</t>
+          <t>Сантехнические работы</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -5797,20 +7364,20 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>замена труб в ванной</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -5818,21 +7385,27 @@
           <t>Тонко</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/prihozhey/</t>
+          <t>/design/vannoy/</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Ремонт прихожей и коридора</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5844,39 +7417,49 @@
         <v>7</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора в квартире</t>
+          <t>дизайн проект ванной</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>/design/spalni/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Натяжные потолки</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Дизайн</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5885,42 +7468,48 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>899</v>
+        <v>57</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект спальни</t>
+          <t>ремонт натяжных потолков после залива цена</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Рабочее ядро</t>
-        </is>
-      </c>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/studiya/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартиры-студии</t>
+          <t>Выравнивание стен</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5929,20 +7518,20 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>сколько стоит выравнивание стен</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5950,16 +7539,22 @@
           <t>Тонко</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/gostinoy/</t>
+          <t>/remont-kvartir/vtorichka/</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ремонт гостиной</t>
+          <t>Ремонт квартиры на вторичке</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -5973,37 +7568,47 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Технический аудит квартиры</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>/design/detskoy/</t>
+          <t>/design/ofisov/</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -6017,42 +7622,52 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>407</v>
+        <v>44</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект детской комнаты</t>
+          <t>дизайн проект офиса</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Рабочее ядро</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/chistovoy/</t>
+          <t>/design/kuhni/</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Чистовая отделка квартиры</t>
+          <t>Дизайн кухни</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -6061,42 +7676,52 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>арт дизайн кухни</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>/priemka/bez-otdelki/</t>
+          <t>/remont-kvartir/stalinka/</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Ремонт в сталинке</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Приёмка</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -6108,34 +7733,44 @@
         <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>приемка квартиры в новостройке без отделки</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/detskoy/</t>
+          <t>/remont-kvartir/3-komnatnoy/</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Ремонт детской комнаты</t>
+          <t>Ремонт трёхкомнатной квартиры</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -6149,42 +7784,52 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H43" s="2" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>ремонт детской комнаты</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>/design/gostinoy/</t>
+          <t>/remont-kvartir/chernovoy/</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Черновой ремонт квартиры</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Дизайн</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -6193,37 +7838,47 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>335</v>
+        <v>41</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект гостиной</t>
+          <t>черновой ремонт под ключ с материалами цена</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Рабочее ядро</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/4-komnatnoy/</t>
+          <t>/remont-kvartir/hrushchevka/</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Ремонт четырёхкомнатной квартиры</t>
+          <t>Ремонт в хрущёвке</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -6233,125 +7888,159 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Не создавать</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>ремонт 4 комнатной квартиры</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Спроса нет</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>/komplektaciya/</t>
+          <t>/remont-kvartir/prihozhey/</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Ремонт прихожей и коридора</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="H46" s="2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>комплектация интерьера</t>
+          <t>ремонт коридора в квартире</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/design/spalni/</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>дизайн проект спальни</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir/spalni/</t>
+          <t>/remont-kvartir/studiya/</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ремонт спальни</t>
+          <t>Ремонт квартиры-студии</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -6365,37 +8054,47 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Интент информационный</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>/design/prihozhey/</t>
+          <t>/design/detskoy/</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6409,42 +8108,52 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>870</v>
+        <v>20</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>прихожая дизайн</t>
+          <t>дизайн проект детской комнаты</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Интент информационный</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>/design/studii/</t>
+          <t>/remont-kvartir/chistovoy/</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Чистовая отделка квартиры</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Дизайн</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6453,42 +8162,52 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>дизайн студии 25 кв м</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Интент информационный</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>/design/kommercheskih-pomesheniy/</t>
+          <t>/remont-kvartir/gostinoy/</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
+          <t>Ремонт гостиной</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6497,38 +8216,52 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>ремонт гостиной</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>/priemka/s-otdelkoy/</t>
+          <t>/remont-kvartir/panelnyy-dom/</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Ремонт в панельном доме</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Приёмка</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6537,38 +8270,52 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>/priemka/v-zhk-shablon/</t>
+          <t>/remont-kvartir/posle-zaliva/</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Ремонт после залива и пожара</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Приёмка</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6577,82 +8324,106 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>ремонт после пожара</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-domov/</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Сантехнические работы</t>
+          <t>Ремонт домов и коттеджей</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Ремонт домов</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Не создавать</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>сантехнические работы это</t>
+          <t>ремонт квартир и коттеджей</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Спроса нет</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Выезд инженера</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/design/kommercheskih-pomesheniy/</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6661,38 +8432,52 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>дизайн проект кафе</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/priemka/bez-otdelki/</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Приёмка</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -6701,203 +8486,273 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>приемка квартиры в новостройке без отделки</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Записаться на приёмку</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Посчитать ремонт после приёмки</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>/faq/</t>
+          <t>/komplektaciya/</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Редирект</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>комплектация дизайн проекта</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Связаться с инженером</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Посетить шоурум</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>/o-kompanii/</t>
+          <t>/remont-kvartir/detskoy/</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Ремонт детской комнаты</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>ремонт детской комнаты</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Спроса нет</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>/kontakty/</t>
+          <t>/design/gostinoy/</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Дизайн</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>дизайн проект гостиной</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Спроса нет</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>/partneram/</t>
+          <t>/remont-kvartir/spalni/</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Ремонт спальни</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>ремонт спальной комнаты</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Тонко</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
@@ -6918,33 +8773,43 @@
           <t>Спроса не найдено</t>
         </is>
       </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Вызвать замерщика</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>/politika-konfidencialnosti/</t>
+          <t>/remont-kvartir/pod-sdachu/</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Ремонт под сдачу в аренду</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Служебные</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>0</v>
@@ -6952,32 +8817,46 @@
       <c r="H62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>ремонт квартиры под сдачу</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Интент информационный</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>/soglasie-na-obrabotku/</t>
+          <t>/remont-kvartir/garderobnoy/</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Ремонт гардеробной</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Служебные</t>
+          <t>Ремонт квартир</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
@@ -6998,26 +8877,36 @@
           <t>Спроса не найдено</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Квиз-калькулятор ремонта</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>/spasibo/</t>
+          <t>/remont-kommercheskih-pomescheniy/</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Спасибо за заявку</t>
+          <t>Ремонт коммерческих помещений</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Служебные</t>
+          <t>Коммерция</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Не создавать</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
@@ -7038,9 +8927,1015 @@
           <t>Спроса не найдено</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Выезд инженера</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>/design/prihozhey/</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн прихожей и коридора</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Не создавать</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Спроса не найдено</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>/design/studii/</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн квартиры-студии</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Не создавать</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Спроса не найдено</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный выезд дизайнера</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Квиз по дизайн-проекту</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>/priemka/s-otdelkoy/</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартиры с отделкой</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Спроса не найдено</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Записаться на приёмку</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Посчитать ремонт после приёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>/priemka/v-zhk-shablon/</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка в ЖК (шаблон)</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Спроса не найдено</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Записаться на приёмку</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Посчитать ремонт после приёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Доверие</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Доверие</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>/faq/</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Доверие</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>/o-kompanii/</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>О компании</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Доверие</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>/kontakty/</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Доверие</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>/partneram/</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Доверие</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Редирект</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Спроса не найдено</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Стать партнёром</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>/blog/</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Блог</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Доверие</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>/politika-konfidencialnosti/</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Служебные</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Редирект</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>/soglasie-na-obrabotku/</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Служебные</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Редирект</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>/spasibo/</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за заявку</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Служебные</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J64"/>
+  <autoFilter ref="A1:L78"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Строка шапки</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Пункт</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Адрес</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя, утилитарная</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Блог</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>/blog/</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Страницы доверия и блог вынесены наверх по образцу domeo.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя, утилитарная</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Страницы доверия и блог вынесены наверх по образцу domeo.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя, утилитарная</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>/faq/</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Страницы доверия и блог вынесены наверх по образцу domeo.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя, утилитарная</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>/partneram/</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Страницы доверия и блог вынесены наверх по образцу domeo.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя, утилитарная</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>О компании</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>/o-kompanii/</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Страницы доверия и блог вынесены наверх по образцу domeo.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Верхняя, утилитарная</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>/kontakty/</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Страницы доверия и блог вынесены наверх по образцу domeo.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kvartir/</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Выпадающий список, 36 пунктов</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>/design/</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Выпадающий список, 11 пунктов</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>/komplektaciya/</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Без выпадающего списка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>/priemka/</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Выпадающий список, 3 пунктов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>— раздел меню, своей страницы нет</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Выпадающий список, 12 пунктов</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Без выпадающего списка</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Вызвать замерщика</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Кнопка справа от меню, открывает попап заявки</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
+++ b/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перелинковка" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Структура сайта'!$A$1:$G$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Структура меню'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Структура сайта'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Структура меню'!$A$1:$E$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Мета-теги'!$A$1:$G$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спрос по страницам'!$A$1:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Шапка сайта'!$A$1:$F$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Шапка сайта'!$A$1:$F$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Иерархия в админке'!$A$1:$F$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Перелинковка'!$A$1:$E$398</definedName>
   </definedNames>
@@ -447,16 +447,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.1" customWidth="1" min="1" max="1"/>
     <col width="36.6" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="54.1" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18.6" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18.6" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +473,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>адрес в шаблоне</t>
+          <t>Адрес на сайте</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -482,15 +483,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Родительская категория</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Текст</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Статус SEO текста</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Дата внедрения</t>
         </is>
@@ -520,6 +526,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -529,7 +536,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>remont-kvartir-pod-klyuch</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -538,9 +545,14 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -550,7 +562,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>remont-kvartiry-v-novostrojke</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -559,9 +571,14 @@
           <t>Ремонт квартиры в новостройке</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -571,7 +588,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>remont-kvartiry-na-vtorichke</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
@@ -580,9 +597,14 @@
           <t>Ремонт квартиры на вторичке</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -592,7 +614,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>kapitalnyj-remont-kvartiry</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -601,9 +623,14 @@
           <t>Капитальный ремонт квартиры</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -613,7 +640,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>kosmeticheskij-remont-kvartiry</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
@@ -622,9 +649,14 @@
           <t>Косметический ремонт квартиры</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -634,7 +666,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>dizajnerskij-remont-kvartiry</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -643,9 +675,14 @@
           <t>Дизайнерский ремонт квартиры</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -655,7 +692,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>chernovoj-remont-kvartiry</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
@@ -664,9 +701,14 @@
           <t>Черновой ремонт квартиры</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -676,7 +718,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>chistovaya-otdelka-kvartiry</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -685,9 +727,14 @@
           <t>Чистовая отделка квартиры</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -697,7 +744,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>evroremont-kvartiry</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -706,9 +753,14 @@
           <t>Евроремонт квартиры</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -718,7 +770,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>remont-kvartiry-studii</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -727,9 +779,14 @@
           <t>Ремонт квартиры-студии</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -739,7 +796,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>remont-odnokomnatnoj-kvartiry</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
@@ -748,9 +805,14 @@
           <t>Ремонт однокомнатной квартиры</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -760,7 +822,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>remont-dvuhkomnatnoj-kvartiry</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -769,9 +831,14 @@
           <t>Ремонт двухкомнатной квартиры</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -781,7 +848,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>remont-tryohkomnatnoj-kvartiry</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -790,9 +857,14 @@
           <t>Ремонт трёхкомнатной квартиры</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -802,7 +874,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>remont-kuhni</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -811,9 +883,14 @@
           <t>Ремонт кухни</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -823,7 +900,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>remont-vannoj-komnaty</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
@@ -832,9 +909,14 @@
           <t>Ремонт ванной комнаты</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -844,7 +926,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>remont-sanuzla</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -853,9 +935,14 @@
           <t>Ремонт санузла</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -865,7 +952,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>remont-spalni</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
@@ -874,9 +961,14 @@
           <t>Ремонт спальни</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -886,7 +978,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>remont-gostinoj</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -895,9 +987,14 @@
           <t>Ремонт гостиной</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -907,7 +1004,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>/remont-detskoj-komnaty/</t>
+          <t>remont-detskoj-komnaty</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
@@ -916,9 +1013,14 @@
           <t>Ремонт детской комнаты</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -928,7 +1030,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>remont-prihozhej-i-koridora</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -937,9 +1039,14 @@
           <t>Ремонт прихожей и коридора</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -949,7 +1056,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>remont-balkona-i-lodzhii</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
@@ -958,9 +1065,14 @@
           <t>Ремонт балкона и лоджии</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -970,7 +1082,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>/tseny-na-remont-kvartir/</t>
+          <t>tseny-na-remont-kvartir</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
@@ -979,9 +1091,14 @@
           <t>Цены на ремонт квартир</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -991,7 +1108,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>remont-v-zhk-shablon</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
@@ -1000,9 +1117,14 @@
           <t>Ремонт в ЖК (шаблон)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1012,7 +1134,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>elitnyj-remont-kvartir</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
@@ -1021,9 +1143,14 @@
           <t>Элитный ремонт квартир</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1033,7 +1160,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>nedorogoj-remont-kvartir</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
@@ -1042,9 +1169,14 @@
           <t>Недорогой ремонт квартир</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1054,7 +1186,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>remont-v-hrushchyovke</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
@@ -1063,9 +1195,14 @@
           <t>Ремонт в хрущёвке</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1075,7 +1212,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>remont-v-stalinke</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
@@ -1084,9 +1221,14 @@
           <t>Ремонт в сталинке</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1096,7 +1238,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>remont-v-panelnom-dome</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -1105,9 +1247,14 @@
           <t>Ремонт в панельном доме</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1117,7 +1264,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>remont-kvartir-po-stilyu</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
@@ -1126,9 +1273,14 @@
           <t>Ремонт квартир по стилю</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1138,7 +1290,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>remont-tualeta</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -1147,9 +1299,14 @@
           <t>Ремонт туалета</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1159,7 +1316,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>remont-posle-zaliva-i-pozhara</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
@@ -1168,9 +1325,14 @@
           <t>Ремонт после залива и пожара</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1180,7 +1342,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>remont-pod-sdachu-v-arendu</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -1189,9 +1351,14 @@
           <t>Ремонт под сдачу в аренду</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1201,7 +1368,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/remont-po-dizajn-proektu/</t>
+          <t>remont-po-dizajn-proektu</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
@@ -1210,9 +1377,14 @@
           <t>Ремонт по дизайн-проекту</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1222,7 +1394,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/remont-garderobnoj/</t>
+          <t>remont-garderobnoj</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -1231,9 +1403,14 @@
           <t>Ремонт гардеробной</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1243,7 +1420,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>remont-domov-i-kottedzhej</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
@@ -1252,9 +1429,14 @@
           <t>Ремонт домов и коттеджей</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1264,7 +1446,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>remont-kommercheskih-pomeshchenij</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
@@ -1273,9 +1455,14 @@
           <t>Ремонт коммерческих помещений</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1285,7 +1472,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>tyoplyj-pol</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
@@ -1294,9 +1481,14 @@
           <t>Тёплый пол</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1306,7 +1498,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>dizajn-interera</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1319,9 +1511,14 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1331,7 +1528,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>dizajn-interera-kvartiry</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
@@ -1340,9 +1537,14 @@
           <t>Дизайн интерьера квартиры</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1352,7 +1554,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>dizajn-kuhni</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
@@ -1361,9 +1563,14 @@
           <t>Дизайн кухни</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1373,7 +1580,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>dizajn-vannoj-komnaty</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
@@ -1382,9 +1589,14 @@
           <t>Дизайн ванной комнаты</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1394,7 +1606,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>dizajn-spalni</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
@@ -1403,9 +1615,14 @@
           <t>Дизайн спальни</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1415,7 +1632,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-gostinoj/</t>
+          <t>dizajn-gostinoj</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
@@ -1424,9 +1641,14 @@
           <t>Дизайн гостиной</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1436,7 +1658,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>dizajn-detskoj-komnaty</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
@@ -1445,9 +1667,14 @@
           <t>Дизайн детской комнаты</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1457,7 +1684,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-prihozhej-i-koridora/</t>
+          <t>dizajn-prihozhej-i-koridora</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
@@ -1466,9 +1693,14 @@
           <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1478,7 +1710,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kvartiry-studii/</t>
+          <t>dizajn-kvartiry-studii</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
@@ -1487,9 +1719,14 @@
           <t>Дизайн квартиры-студии</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1499,7 +1736,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>dizajn-interera-ofisa</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
@@ -1508,9 +1745,14 @@
           <t>Дизайн интерьера офиса</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1520,7 +1762,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>dizajn-interera-doma</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
@@ -1529,9 +1771,14 @@
           <t>Дизайн интерьера дома</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1541,7 +1788,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+          <t>dizajn-kommercheskih-pomeshchenij</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
@@ -1550,9 +1797,14 @@
           <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1562,7 +1814,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>priyomka-kvartir-v-novostrojke</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1575,9 +1827,14 @@
           <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1587,7 +1844,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>priyomka-kvartiry-bez-otdelki</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
@@ -1596,9 +1853,14 @@
           <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1608,7 +1870,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+          <t>priyomka-kvartiry-s-otdelkoj</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
@@ -1617,9 +1879,14 @@
           <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1629,7 +1896,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-v-zhk-shablon/</t>
+          <t>priyomka-v-zhk-shablon</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
@@ -1638,9 +1905,14 @@
           <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1650,7 +1922,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>komplektatsiya-kvartiry</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1663,9 +1935,14 @@
           <t>Комплектация квартиры</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1675,7 +1952,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>pereplanirovka-kvartiry</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
@@ -1684,9 +1961,14 @@
           <t>Перепланировка квартиры</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1696,7 +1978,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>mehanizirovannaya-shtukaturka</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
@@ -1705,9 +1987,14 @@
           <t>Механизированная штукатурка</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1717,7 +2004,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>styazhka-pola</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
@@ -1726,9 +2013,14 @@
           <t>Стяжка пола</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1738,7 +2030,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>elektromontazhnye-raboty</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
@@ -1747,9 +2039,14 @@
           <t>Электромонтажные работы</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1759,7 +2056,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>santehnicheskie-raboty</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
@@ -1768,9 +2065,14 @@
           <t>Сантехнические работы</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1780,7 +2082,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>demontazhnye-raboty</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
@@ -1789,9 +2091,14 @@
           <t>Демонтажные работы</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1801,7 +2108,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>shumoizolyatsiya-kvartiry</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
@@ -1810,9 +2117,14 @@
           <t>Шумоизоляция квартиры</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1822,7 +2134,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>malyarnye-raboty-i-poklejka-oboev</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
@@ -1831,9 +2143,14 @@
           <t>Малярные работы и поклейка обоев</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1843,7 +2160,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>ukladka-plitki</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
@@ -1852,9 +2169,14 @@
           <t>Укладка плитки</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1864,7 +2186,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>natyazhnye-potolki</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
@@ -1873,9 +2195,14 @@
           <t>Натяжные потолки</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1885,7 +2212,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>vyravnivanie-sten</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
@@ -1894,9 +2221,14 @@
           <t>Выравнивание стен</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1906,7 +2238,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>inzhenernye-sistemy</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
@@ -1915,9 +2247,14 @@
           <t>Инженерные системы</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1927,7 +2264,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>ustanovka-konditsionerov</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
@@ -1936,9 +2273,14 @@
           <t>Установка кондиционеров</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1948,7 +2290,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>ventilyatsiya</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
@@ -1957,9 +2299,14 @@
           <t>Вентиляция</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1969,7 +2316,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>umnyj-dom</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
@@ -1978,9 +2325,14 @@
           <t>Умный дом</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1990,7 +2342,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>otoplenie-i-radiatory</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
@@ -1999,9 +2351,14 @@
           <t>Отопление и радиаторы</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2011,7 +2368,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>/otdelochnye-raboty/</t>
+          <t>otdelochnye-raboty</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
@@ -2020,9 +2377,14 @@
           <t>Отделочные работы</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2032,7 +2394,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>dekorativnaya-shtukaturka</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
@@ -2041,9 +2403,14 @@
           <t>Декоративная штукатурка</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2053,7 +2420,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>/demontazh-i-chernovye-raboty/</t>
+          <t>demontazh-i-chernovye-raboty</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
@@ -2062,9 +2429,14 @@
           <t>Демонтаж и черновые работы</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2074,7 +2446,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>portfolio</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
@@ -2083,9 +2455,14 @@
           <t>Портфолио</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2095,7 +2472,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>otzyvy</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
@@ -2104,9 +2481,14 @@
           <t>Отзывы</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2116,7 +2498,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>/faq/</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
@@ -2125,9 +2507,14 @@
           <t>Вопросы и ответы</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2137,7 +2524,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>/o-kompanii/</t>
+          <t>o-kompanii</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr"/>
@@ -2146,9 +2533,14 @@
           <t>О компании</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2158,7 +2550,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>/kontakty/</t>
+          <t>kontakty</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr"/>
@@ -2167,9 +2559,14 @@
           <t>Контакты</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2179,7 +2576,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>/partners/</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -2192,9 +2589,14 @@
           <t>Партнёрам</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2204,7 +2606,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
@@ -2213,9 +2615,14 @@
           <t>Блог</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2225,7 +2632,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>/politika-konfidencialnosti/</t>
+          <t>politika-konfidencialnosti</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -2238,9 +2645,14 @@
           <t>Политика конфиденциальности</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2250,7 +2662,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>/soglasie-na-obrabotku/</t>
+          <t>soglasie-na-obrabotku</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -2263,9 +2675,14 @@
           <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2275,7 +2692,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>/spasibo/</t>
+          <t>spasibo</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
@@ -2284,12 +2701,17 @@
           <t>Спасибо за заявку</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85"/>
+  <autoFilter ref="A1:H85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2300,951 +2722,2385 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25.8" customWidth="1" min="1" max="1"/>
-    <col width="25.8" customWidth="1" min="2" max="2"/>
-    <col width="25.8" customWidth="1" min="3" max="3"/>
-    <col width="25.8" customWidth="1" min="4" max="4"/>
-    <col width="25.8" customWidth="1" min="5" max="5"/>
-    <col width="25.8" customWidth="1" min="6" max="6"/>
-    <col width="25.8" customWidth="1" min="7" max="7"/>
-    <col width="25.8" customWidth="1" min="8" max="8"/>
-    <col width="25.8" customWidth="1" min="9" max="9"/>
-    <col width="25.8" customWidth="1" min="10" max="10"/>
-    <col width="25.8" customWidth="1" min="11" max="11"/>
-    <col width="25.8" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ремонт квартир</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Дизайн интерьера</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Комплектация</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Приёмка</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Услуги</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Портфолио</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Блог</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Отзывы</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Вопросы и ответы</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Партнёрам</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>О компании</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Контакты</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Строка шапки</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Пункт меню</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Родительская категория</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Страница</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Адрес</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>По виду ремонта</t>
+          <t>Верхняя, утилитарная</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>По объекту</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+          <t>Блог</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Без отделки</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>/blog/</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Новостройка</t>
+          <t>Верхняя, утилитарная</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Квартира</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>С отделкой</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Электромонтаж</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Вторичка</t>
+          <t>Верхняя, утилитарная</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Квартира-студия</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>По ЖК</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Сантехника</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>/faq/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Капитальный</t>
+          <t>Верхняя, утилитарная</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Дом</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+          <t>Партнёрам</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Вентиляция</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>/partners/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Косметический</t>
+          <t>Верхняя, утилитарная</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Офис</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>О компании</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>О компании</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Кондиционирование</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>/o-kompanii/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Дизайнерский</t>
+          <t>Верхняя, утилитарная</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Коммерческие помещения</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Тёплый пол</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>/kontakty/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>По дизайн-проекту</t>
+          <t>Основная, коммерческая</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>По помещениям</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>Ремонт квартир</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Умный дом</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>/remont-kvartir-pod-klyuch/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Черновой</t>
+          <t>Основная, коммерческая</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Кухня</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Отопление</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Чистовая отделка</t>
+          <t>Основная, коммерческая</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Ванная комната</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+          <t>Новостройка</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартиры в новостройке</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>/remont-kvartiry-v-novostrojke/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Евроремонт</t>
+          <t>Основная, коммерческая</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Спальня</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>Вторичка</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартиры на вторичке</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>/remont-kvartiry-na-vtorichke/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Элитный</t>
+          <t>Основная, коммерческая</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Гостиная</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>Капитальный</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Капитальный ремонт квартиры</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и обои</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>/kapitalnyj-remont-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Недорогой</t>
+          <t>Основная, коммерческая</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Детская комната</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>Косметический</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Косметический ремонт квартиры</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Под сдачу</t>
+          <t>Основная, коммерческая</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Прихожая и коридор</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Дизайнерский</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Дизайнерский ремонт квартиры</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>/dizajnerskij-remont-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>После залива и пожара</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Черновой</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Черновой ремонт квартиры</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Декоративная штукатурка</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>/chernovoj-remont-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>По стилю</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Чистовая отделка</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Чистовая отделка квартиры</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>/chistovaya-otdelka-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>По числу комнат</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Евроремонт</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Евроремонт квартиры</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>/evroremont-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Студия</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Элитный</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Элитный ремонт квартир</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>/elitnyj-remont-kvartir/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Однокомнатная</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Недорогой</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Недорогой ремонт квартир</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>/nedorogoj-remont-kvartir/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Двухкомнатная</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Под сдачу</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт под сдачу в аренду</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>/remont-pod-sdachu-v-arendu/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Трёхкомнатная</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>После залива и пожара</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт после залива и пожара</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>По типу дома</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>По стилю</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>По виду ремонта</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир по стилю</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>/remont-kvartir-po-stilyu/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Хрущёвка</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>По числу комнат</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>— только заголовок</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Сталинка</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Студия</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>По числу комнат</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартиры-студии</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kvartiry-studii/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Панельный дом</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Однокомнатная</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>По числу комнат</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт однокомнатной квартиры</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>По помещениям</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Двухкомнатная</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>По числу комнат</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт двухкомнатной квартиры</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Кухня</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Трёхкомнатная</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>По числу комнат</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт трёхкомнатной квартиры</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Ванная комната</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>По типу дома</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>— только заголовок</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Санузел</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Хрущёвка</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>По типу дома</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в хрущёвке</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>/remont-v-hrushchyovke/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Туалет</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Сталинка</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>По типу дома</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в сталинке</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>/remont-v-stalinke/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Спальня</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Панельный дом</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>По типу дома</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в панельном доме</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>/remont-v-panelnom-dome/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Гостиная</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>— только заголовок</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Детская комната</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Кухня</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт кухни</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kuhni/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Прихожая и коридор</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Ванная комната</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт ванной комнаты</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>/remont-vannoj-komnaty/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Балкон и лоджия</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Санузел</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт санузла</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>/remont-sanuzla/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Гардеробная</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Туалет</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт туалета</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>/remont-tualeta/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Спальня</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт спальни</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>/remont-spalni/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Цены</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Гостиная</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт гостиной</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>/remont-gostinoj/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>По ЖК</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Детская комната</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт детской комнаты</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>/remont-detskoj-komnaty/</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Дома и коттеджи</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Прихожая и коридор</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт прихожей и коридора</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>/remont-prihozhej-i-koridora/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Балкон и лоджия</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт балкона и лоджии</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>/remont-balkona-i-lodzhii/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Гардеробная</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт гардеробной</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>/remont-garderobnoj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Цены</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Цены на ремонт квартир</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>/tseny-na-remont-kvartir/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>По ЖК</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в ЖК (шаблон)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>/remont-v-zhk-shablon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Дома и коттеджи</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт домов и коттеджей</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>/remont-domov-i-kottedzhej/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>Коммерческие помещения</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт коммерческих помещений</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-interera/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>По объекту</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Квартира</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>По объекту</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера квартиры</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-interera-kvartiry/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Квартира-студия</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>По объекту</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн квартиры-студии</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-kvartiry-studii/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Дом</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>По объекту</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера дома</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-interera-doma/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Офис</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>По объекту</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера офиса</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-interera-ofisa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Коммерческие помещения</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>По объекту</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн коммерческих помещений</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Кухня</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн кухни</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-kuhni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Ванная комната</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн ванной комнаты</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-vannoj-komnaty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Спальня</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн спальни</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-spalni/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Гостиная</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн гостиной</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-gostinoj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Детская комната</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн детской комнаты</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-detskoj-komnaty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Прихожая и коридор</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>По помещениям</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн прихожей и коридора</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-prihozhej-i-koridora/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация квартиры</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>/komplektatsiya-kvartiry/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Без отделки</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартиры без отделки</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>С отделкой</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартиры с отделкой</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>По ЖК</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка в ЖК (шаблон)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>/priyomka-v-zhk-shablon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>— раздел меню</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>/inzhenernye-sistemy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Электромонтаж</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Электромонтажные работы</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>/elektromontazhnye-raboty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Сантехника</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Сантехнические работы</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>/santehnicheskie-raboty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Вентиляция</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Вентиляция</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>/ventilyatsiya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Кондиционирование</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Установка кондиционеров</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>/ustanovka-konditsionerov/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Тёплый пол</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Тёплый пол</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>/tyoplyj-pol/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Умный дом</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Умный дом</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>/umnyj-dom/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Отопление</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Отопление и радиаторы</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>/otoplenie-i-radiatory/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция квартиры</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>/shumoizolyatsiya-kvartiry/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>/otdelochnye-raboty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и обои</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и поклейка обоев</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>/ukladka-plitki/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>/natyazhnye-potolki/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Декоративная штукатурка</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Декоративная штукатурка</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>/dekorativnaya-shtukaturka/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>/demontazh-i-chernovye-raboty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Демонтажные работы</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>/demontazhnye-raboty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Стяжка пола</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Стяжка пола</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>/styazhka-pola/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Механизированная штукатурка</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Механизированная штукатурка</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>/mehanizirovannaya-shtukaturka/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>/vyravnivanie-sten/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Перепланировка</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Перепланировка квартиры</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>/pereplanirovka-kvartiry/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Шапка сайта</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Основная, коммерческая</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Вызвать замерщика</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Кнопка</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Попап заявки</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:E89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10379,7 +12235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10824,17 +12680,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>По дизайн-проекту</t>
+          <t>Черновой</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Ремонт по дизайн-проекту</t>
+          <t>Черновой ремонт квартиры</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>/remont-po-dizajn-proektu/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -10856,17 +12712,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Черновой</t>
+          <t>Чистовая отделка</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Черновой ремонт квартиры</t>
+          <t>Чистовая отделка квартиры</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -10888,17 +12744,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Чистовая отделка</t>
+          <t>Евроремонт</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Чистовая отделка квартиры</t>
+          <t>Евроремонт квартиры</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -10920,17 +12776,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Евроремонт</t>
+          <t>Элитный</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Евроремонт квартиры</t>
+          <t>Элитный ремонт квартир</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
     </row>
@@ -10952,17 +12808,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Элитный</t>
+          <t>Недорогой</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Элитный ремонт квартир</t>
+          <t>Недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
     </row>
@@ -10984,17 +12840,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Недорогой</t>
+          <t>Под сдачу</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Недорогой ремонт квартир</t>
+          <t>Ремонт под сдачу в аренду</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
     </row>
@@ -11016,17 +12872,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Под сдачу</t>
+          <t>После залива и пожара</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Ремонт под сдачу в аренду</t>
+          <t>Ремонт после залива и пожара</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
     </row>
@@ -11048,17 +12904,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>После залива и пожара</t>
+          <t>По стилю</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Ремонт после залива и пожара</t>
+          <t>Ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
     </row>
@@ -11075,24 +12931,20 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>По виду ремонта</t>
+          <t>По числу комнат</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>По стилю</t>
+          <t>По числу комнат (заголовок группы)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир по стилю</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>/remont-kvartir-po-stilyu/</t>
-        </is>
-      </c>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -11112,15 +12964,19 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>По числу комнат (заголовок группы)</t>
+          <t>Студия</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>— только заголовок</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+          <t>Ремонт квартиры-студии</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kvartiry-studii/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -11140,17 +12996,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Студия</t>
+          <t>Однокомнатная</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартиры-студии</t>
+          <t>Ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -11172,17 +13028,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Однокомнатная</t>
+          <t>Двухкомнатная</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ремонт однокомнатной квартиры</t>
+          <t>Ремонт двухкомнатной квартиры</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -11204,17 +13060,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Двухкомнатная</t>
+          <t>Трёхкомнатная</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Ремонт двухкомнатной квартиры</t>
+          <t>Ремонт трёхкомнатной квартиры</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -11231,24 +13087,20 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>По числу комнат</t>
+          <t>По типу дома</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Трёхкомнатная</t>
+          <t>По типу дома (заголовок группы)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Ремонт трёхкомнатной квартиры</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
-        </is>
-      </c>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -11268,15 +13120,19 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>По типу дома (заголовок группы)</t>
+          <t>Хрущёвка</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>— только заголовок</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+          <t>Ремонт в хрущёвке</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>/remont-v-hrushchyovke/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -11296,17 +13152,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Хрущёвка</t>
+          <t>Сталинка</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Ремонт в хрущёвке</t>
+          <t>Ремонт в сталинке</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
     </row>
@@ -11328,17 +13184,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Сталинка</t>
+          <t>Панельный дом</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Ремонт в сталинке</t>
+          <t>Ремонт в панельном доме</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
     </row>
@@ -11355,24 +13211,20 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>По типу дома</t>
+          <t>По помещениям</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Панельный дом</t>
+          <t>По помещениям (заголовок группы)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Ремонт в панельном доме</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>/remont-v-panelnom-dome/</t>
-        </is>
-      </c>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -11392,15 +13244,19 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>По помещениям (заголовок группы)</t>
+          <t>Кухня</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>— только заголовок</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
+          <t>Ремонт кухни</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kuhni/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -11420,17 +13276,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Кухня</t>
+          <t>Ванная комната</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Ремонт кухни</t>
+          <t>Ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
     </row>
@@ -11452,17 +13308,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Ванная комната</t>
+          <t>Санузел</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Ремонт ванной комнаты</t>
+          <t>Ремонт санузла</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
     </row>
@@ -11484,17 +13340,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Санузел</t>
+          <t>Туалет</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Ремонт санузла</t>
+          <t>Ремонт туалета</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
     </row>
@@ -11516,17 +13372,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Туалет</t>
+          <t>Спальня</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Ремонт туалета</t>
+          <t>Ремонт спальни</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
     </row>
@@ -11548,17 +13404,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Спальня</t>
+          <t>Гостиная</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Ремонт спальни</t>
+          <t>Ремонт гостиной</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
     </row>
@@ -11580,17 +13436,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Гостиная</t>
+          <t>Детская комната</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ремонт гостиной</t>
+          <t>Ремонт детской комнаты</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-detskoj-komnaty/</t>
         </is>
       </c>
     </row>
@@ -11612,17 +13468,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Детская комната</t>
+          <t>Прихожая и коридор</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Ремонт детской комнаты</t>
+          <t>Ремонт прихожей и коридора</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/remont-detskoj-komnaty/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
     </row>
@@ -11644,17 +13500,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Прихожая и коридор</t>
+          <t>Балкон и лоджия</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Ремонт прихожей и коридора</t>
+          <t>Ремонт балкона и лоджии</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
     </row>
@@ -11676,17 +13532,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Балкон и лоджия</t>
+          <t>Гардеробная</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Ремонт балкона и лоджии</t>
+          <t>Ремонт гардеробной</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/remont-garderobnoj/</t>
         </is>
       </c>
     </row>
@@ -11703,24 +13559,20 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>По помещениям</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Гардеробная</t>
+          <t>Прочее (заголовок группы)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Ремонт гардеробной</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>/remont-garderobnoj/</t>
-        </is>
-      </c>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -11740,15 +13592,19 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Прочее (заголовок группы)</t>
+          <t>Цены</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>— только заголовок</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
+          <t>Цены на ремонт квартир</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>/tseny-na-remont-kvartir/</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -11768,17 +13624,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Цены</t>
+          <t>По ЖК</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Цены на ремонт квартир</t>
+          <t>Ремонт в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>/tseny-na-remont-kvartir/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
     </row>
@@ -11800,17 +13656,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>По ЖК</t>
+          <t>Дома и коттеджи</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Ремонт в ЖК (шаблон)</t>
+          <t>Ремонт домов и коттеджей</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-domov-i-kottedzhej/</t>
         </is>
       </c>
     </row>
@@ -11832,17 +13688,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Дома и коттеджи</t>
+          <t>Коммерческие помещения</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Ремонт домов и коттеджей</t>
+          <t>Ремонт коммерческих помещений</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
     </row>
@@ -11854,27 +13710,23 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ремонт квартир</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Коммерческие помещения</t>
+          <t>Дизайн интерьера</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Ремонт коммерческих помещений</t>
+          <t>Дизайн интерьера</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
     </row>
@@ -11889,22 +13741,22 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>По объекту</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера</t>
+          <t>По объекту (заголовок группы)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>/dizajn-interera/</t>
-        </is>
-      </c>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11924,15 +13776,19 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>По объекту (заголовок группы)</t>
+          <t>Квартира</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>— только заголовок</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+          <t>Дизайн интерьера квартиры</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-interera-kvartiry/</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -11952,17 +13808,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Квартира</t>
+          <t>Квартира-студия</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера квартиры</t>
+          <t>Дизайн квартиры-студии</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/dizajn-kvartiry-studii/</t>
         </is>
       </c>
     </row>
@@ -11984,17 +13840,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Квартира-студия</t>
+          <t>Дом</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Дизайн интерьера дома</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kvartiry-studii/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
     </row>
@@ -12016,17 +13872,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Дом</t>
+          <t>Офис</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
     </row>
@@ -12048,17 +13904,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Коммерческие помещения</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
     </row>
@@ -12075,24 +13931,20 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>По объекту</t>
+          <t>По помещениям</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Коммерческие помещения</t>
+          <t>По помещениям (заголовок группы)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>/dizajn-kommercheskih-pomeshchenij/</t>
-        </is>
-      </c>
+          <t>— только заголовок</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -12112,15 +13964,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>По помещениям (заголовок группы)</t>
+          <t>Кухня</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>— только заголовок</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>Дизайн кухни</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-kuhni/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -12140,17 +13996,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Кухня</t>
+          <t>Ванная комната</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
     </row>
@@ -12172,17 +14028,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Ванная комната</t>
+          <t>Спальня</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
     </row>
@@ -12204,17 +14060,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Спальня</t>
+          <t>Гостиная</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-gostinoj/</t>
         </is>
       </c>
     </row>
@@ -12236,17 +14092,17 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Гостиная</t>
+          <t>Детская комната</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-gostinoj/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
     </row>
@@ -12268,17 +14124,17 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Детская комната</t>
+          <t>Прихожая и коридор</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/dizajn-prihozhej-i-koridora/</t>
         </is>
       </c>
     </row>
@@ -12290,27 +14146,23 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>По помещениям</t>
-        </is>
-      </c>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Прихожая и коридор</t>
+          <t>Комплектация</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-prihozhej-i-koridora/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -12322,23 +14174,23 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Комплектация</t>
+          <t>Приёмка</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Комплектация</t>
+          <t>Приёмка</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
     </row>
@@ -12356,17 +14208,17 @@
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Приёмка</t>
+          <t>Без отделки</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
     </row>
@@ -12384,17 +14236,17 @@
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Без отделки</t>
+          <t>С отделкой</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
     </row>
@@ -12412,17 +14264,17 @@
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>С отделкой</t>
+          <t>По ЖК</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
     </row>
@@ -12434,25 +14286,21 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>По ЖК</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>/priyomka-v-zhk-shablon/</t>
-        </is>
-      </c>
+          <t>— раздел меню</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12465,18 +14313,26 @@
           <t>Услуги</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Инженерные системы (заголовок группы, ссылка)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>— раздел меню</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>/inzhenernye-sistemy/</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12496,17 +14352,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы (заголовок группы, ссылка)</t>
+          <t>Электромонтаж</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
+          <t>Электромонтажные работы</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
     </row>
@@ -12528,17 +14384,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Электромонтаж</t>
+          <t>Сантехника</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы</t>
+          <t>Сантехнические работы</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
     </row>
@@ -12560,17 +14416,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Сантехника</t>
+          <t>Вентиляция</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Сантехнические работы</t>
+          <t>Вентиляция</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
     </row>
@@ -12592,17 +14448,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Вентиляция</t>
+          <t>Кондиционирование</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Вентиляция</t>
+          <t>Установка кондиционеров</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
     </row>
@@ -12624,17 +14480,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Кондиционирование</t>
+          <t>Тёплый пол</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Установка кондиционеров</t>
+          <t>Тёплый пол</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
     </row>
@@ -12656,17 +14512,17 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Тёплый пол</t>
+          <t>Умный дом</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Тёплый пол</t>
+          <t>Умный дом</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
     </row>
@@ -12688,17 +14544,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Умный дом</t>
+          <t>Отопление</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Умный дом</t>
+          <t>Отопление и радиаторы</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
     </row>
@@ -12720,17 +14576,17 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Отопление</t>
+          <t>Шумоизоляция</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Отопление и радиаторы</t>
+          <t>Шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -12747,22 +14603,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
+          <t>Отделочные работы</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция</t>
+          <t>Отделочные работы (заголовок группы, ссылка)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Отделочные работы</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/otdelochnye-raboty/</t>
         </is>
       </c>
     </row>
@@ -12784,17 +14640,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы (заголовок группы, ссылка)</t>
+          <t>Малярные работы и обои</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
+          <t>Малярные работы и поклейка обоев</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>/otdelochnye-raboty/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
     </row>
@@ -12816,17 +14672,17 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и обои</t>
+          <t>Укладка плитки</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев</t>
+          <t>Укладка плитки</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
     </row>
@@ -12848,17 +14704,17 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Натяжные потолки</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Натяжные потолки</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
     </row>
@@ -12880,17 +14736,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Декоративная штукатурка</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Декоративная штукатурка</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
     </row>
@@ -12907,22 +14763,22 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Декоративная штукатурка</t>
+          <t>Демонтаж и черновые работы (заголовок группы, ссылка)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Декоративная штукатурка</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/demontazh-i-chernovye-raboty/</t>
         </is>
       </c>
     </row>
@@ -12944,17 +14800,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы (заголовок группы, ссылка)</t>
+          <t>Демонтаж</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>/demontazh-i-chernovye-raboty/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
     </row>
@@ -12976,17 +14832,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
     </row>
@@ -13008,17 +14864,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
     </row>
@@ -13040,17 +14896,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Выравнивание стен</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Выравнивание стен</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
     </row>
@@ -13065,24 +14921,20 @@
           <t>Услуги</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
+      <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Перепланировка</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
     </row>
@@ -13094,23 +14946,23 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
     </row>
@@ -13122,52 +14974,24 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Кнопка</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Вызвать замерщика</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>/portfolio/</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Основная, коммерческая</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Кнопка</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Вызвать замерщика</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
           <t>Попап заявки</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F90"/>
+  <autoFilter ref="A1:F89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
+++ b/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перелинковка" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Структура сайта'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Структура сайта'!$A$1:$L$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Структура меню'!$A$1:$E$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Мета-теги'!$A$1:$G$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спрос по страницам'!$A$1:$L$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Мета-теги'!$A$1:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спрос по страницам'!$A$1:$L$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Шапка сайта'!$A$1:$F$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Иерархия в админке'!$A$1:$F$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Перелинковка'!$A$1:$E$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Иерархия в админке'!$A$1:$F$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Перелинковка'!$A$1:$E$400</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,17 +447,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.1" customWidth="1" min="1" max="1"/>
     <col width="36.6" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="54.1" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18.6" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18.6" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,15 +492,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>1 уровень</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2 уровень</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>3 уровень</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>4 уровень</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Текст</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Статус SEO текста</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Дата внедрения</t>
         </is>
@@ -524,9 +548,17 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -550,9 +582,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -576,9 +616,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартиры в новостройке</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -602,9 +654,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартиры на вторичке</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -628,9 +692,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Капитальный ремонт квартиры</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -654,9 +730,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Косметический ремонт квартиры</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -680,9 +768,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Дизайнерский ремонт квартиры</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -706,9 +806,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Черновой ремонт квартиры</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -732,9 +844,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Чистовая отделка квартиры</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -758,9 +882,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Евроремонт квартиры</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -784,9 +920,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартиры-студии</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -810,9 +958,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт однокомнатной квартиры</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -836,9 +996,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт двухкомнатной квартиры</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -862,9 +1034,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт трёхкомнатной квартиры</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -888,9 +1072,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт кухни</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -914,9 +1110,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт ванной комнаты</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -940,9 +1148,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт санузла</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -966,9 +1186,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт спальни</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -992,9 +1224,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт гостиной</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1018,9 +1262,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт детской комнаты</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1044,9 +1300,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт прихожей и коридора</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1070,9 +1338,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт балкона и лоджии</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1096,9 +1376,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Цены на ремонт квартир</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1122,9 +1414,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в ЖК (шаблон)</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1148,9 +1452,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Элитный ремонт квартир</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1174,9 +1490,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Недорогой ремонт квартир</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1200,9 +1528,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в хрущёвке</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1226,9 +1566,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в сталинке</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1252,9 +1604,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт в панельном доме</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1278,9 +1642,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир по стилю</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1304,9 +1680,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт туалета</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1330,9 +1718,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт после залива и пожара</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1356,9 +1756,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт под сдачу в аренду</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1382,9 +1794,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт по дизайн-проекту</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1408,9 +1832,21 @@
           <t>Ремонт квартир под ключ</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт квартир под ключ</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт гардеробной</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1434,9 +1870,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт домов и коттеджей</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1460,65 +1904,93 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Ремонт коммерческих помещений</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Редирект</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>tyoplyj-pol</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>dizajn-interera</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>/design</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Тёплый пол</t>
+          <t>Дизайн интерьера</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>Главная</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>dizajn-interera</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>/design</t>
-        </is>
-      </c>
+          <t>dizajn-interera-kvartiry</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Дизайн интерьера квартиры</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Главная</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера квартиры</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1528,13 +2000,13 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>dizajn-interera-kvartiry</t>
+          <t>dizajn-kuhni</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера квартиры</t>
+          <t>Дизайн кухни</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1542,9 +2014,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн кухни</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1554,13 +2038,13 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>dizajn-kuhni</t>
+          <t>dizajn-vannoj-komnaty</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1568,9 +2052,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн ванной комнаты</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1580,13 +2076,13 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>dizajn-vannoj-komnaty</t>
+          <t>dizajn-spalni</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1594,9 +2090,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн спальни</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1606,13 +2114,13 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>dizajn-spalni</t>
+          <t>dizajn-gostinoj</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1620,9 +2128,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн гостиной</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1632,13 +2152,13 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>dizajn-gostinoj</t>
+          <t>dizajn-detskoj-komnaty</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1646,9 +2166,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн детской комнаты</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1658,13 +2190,13 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>dizajn-detskoj-komnaty</t>
+          <t>dizajn-prihozhej-i-koridora</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1672,9 +2204,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн прихожей и коридора</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1684,13 +2228,13 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>dizajn-prihozhej-i-koridora</t>
+          <t>dizajn-kvartiry-studii</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Дизайн квартиры-студии</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1698,9 +2242,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн квартиры-студии</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1710,13 +2266,13 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>dizajn-kvartiry-studii</t>
+          <t>dizajn-interera-ofisa</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1724,9 +2280,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера офиса</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1736,13 +2304,13 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>dizajn-interera-ofisa</t>
+          <t>dizajn-interera-doma</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Дизайн интерьера дома</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1750,9 +2318,21 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера дома</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1762,13 +2342,13 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>dizajn-interera-doma</t>
+          <t>dizajn-kommercheskih-pomeshchenij</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1776,65 +2356,97 @@
           <t>Дизайн интерьера</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн интерьера</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Дизайн коммерческих помещений</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Редирект</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>dizajn-kommercheskih-pomeshchenij</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
+          <t>priyomka-kvartir-v-novostrojke</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>/priemka</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
+          <t>Главная</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>priyomka-kvartir-v-novostrojke</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>/priemka</t>
-        </is>
-      </c>
+          <t>priyomka-kvartiry-bez-otdelki</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>Приёмка квартиры без отделки</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Главная</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартиры без отделки</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1844,13 +2456,13 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>priyomka-kvartiry-bez-otdelki</t>
+          <t>priyomka-kvartiry-s-otdelkoj</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1858,9 +2470,21 @@
           <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартиры с отделкой</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1870,13 +2494,13 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>priyomka-kvartiry-s-otdelkoj</t>
+          <t>priyomka-v-zhk-shablon</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1884,55 +2508,75 @@
           <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка в ЖК (шаблон)</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Редирект</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>priyomka-v-zhk-shablon</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
+          <t>komplektatsiya-kvartiry</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>/komplekt</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+          <t>Главная</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация квартиры</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>komplektatsiya-kvartiry</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>/komplekt</t>
-        </is>
-      </c>
+          <t>uslugi</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1940,9 +2584,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1952,23 +2604,35 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>pereplanirovka-kvartiry</t>
+          <t>inzhenernye-sistemy</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Инженерные системы</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1978,23 +2642,39 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>mehanizirovannaya-shtukaturka</t>
+          <t>tyoplyj-pol</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Тёплый пол</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Тёплый пол</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2004,23 +2684,39 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>styazhka-pola</t>
+          <t>elektromontazhnye-raboty</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Электромонтажные работы</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Электромонтажные работы</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2030,13 +2726,13 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>elektromontazhnye-raboty</t>
+          <t>santehnicheskie-raboty</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы</t>
+          <t>Сантехнические работы</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2044,9 +2740,25 @@
           <t>Инженерные системы</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Сантехнические работы</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2056,13 +2768,13 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>santehnicheskie-raboty</t>
+          <t>shumoizolyatsiya-kvartiry</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Сантехнические работы</t>
+          <t>Шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2070,9 +2782,25 @@
           <t>Инженерные системы</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Шумоизоляция квартиры</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2082,23 +2810,39 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>demontazhnye-raboty</t>
+          <t>ustanovka-konditsionerov</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Установка кондиционеров</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Установка кондиционеров</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2108,13 +2852,13 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>shumoizolyatsiya-kvartiry</t>
+          <t>ventilyatsiya</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Вентиляция</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2122,9 +2866,25 @@
           <t>Инженерные системы</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Вентиляция</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2134,23 +2894,39 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>malyarnye-raboty-i-poklejka-oboev</t>
+          <t>umnyj-dom</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев</t>
+          <t>Умный дом</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Умный дом</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2160,23 +2936,39 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ukladka-plitki</t>
+          <t>otoplenie-i-radiatory</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Отопление и радиаторы</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Отопление и радиаторы</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2186,23 +2978,35 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>natyazhnye-potolki</t>
+          <t>otdelochnye-raboty</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Отделочные работы</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
           <t>Отделочные работы</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2212,23 +3016,39 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>vyravnivanie-sten</t>
+          <t>malyarnye-raboty-i-poklejka-oboev</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Малярные работы и поклейка обоев</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Малярные работы и поклейка обоев</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2238,23 +3058,39 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>inzhenernye-sistemy</t>
+          <t>ukladka-plitki</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
+          <t>Укладка плитки</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Укладка плитки</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2264,23 +3100,39 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ustanovka-konditsionerov</t>
+          <t>natyazhnye-potolki</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Установка кондиционеров</t>
+          <t>Натяжные потолки</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Натяжные потолки</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2290,23 +3142,39 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ventilyatsiya</t>
+          <t>dekorativnaya-shtukaturka</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Вентиляция</t>
+          <t>Декоративная штукатурка</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Декоративная штукатурка</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2316,23 +3184,35 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>umnyj-dom</t>
+          <t>demontazh-i-chernovye-raboty</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Умный дом</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2342,23 +3222,39 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>otoplenie-i-radiatory</t>
+          <t>mehanizirovannaya-shtukaturka</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Отопление и радиаторы</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Механизированная штукатурка</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2368,23 +3264,39 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>otdelochnye-raboty</t>
+          <t>styazhka-pola</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Стяжка пола</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2394,23 +3306,39 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>dekorativnaya-shtukaturka</t>
+          <t>demontazhnye-raboty</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Декоративная штукатурка</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Демонтажные работы</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2420,23 +3348,39 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>demontazh-i-chernovye-raboty</t>
+          <t>vyravnivanie-sten</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>Демонтаж и черновые работы</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Главная</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Демонтаж и черновые работы</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2446,23 +3390,35 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>portfolio</t>
+          <t>pereplanirovka-kvartiry</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Перепланировка квартиры</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2472,13 +3428,13 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>otzyvy</t>
+          <t>portfolio</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2486,9 +3442,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2498,13 +3462,13 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>faq</t>
+          <t>otzyvy</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2512,9 +3476,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2524,13 +3496,13 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>o-kompanii</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2538,9 +3510,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2550,13 +3530,13 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>kontakty</t>
+          <t>o-kompanii</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2564,29 +3544,33 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>О компании</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>partners</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>/partners</t>
-        </is>
-      </c>
+          <t>kontakty</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2594,25 +3578,37 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>blog</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr"/>
+          <t>partners</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>/partners</t>
+        </is>
+      </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2620,9 +3616,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Партнёрам</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2632,17 +3636,13 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>politika-konfidencialnosti</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>/politicakonfident</t>
-        </is>
-      </c>
+          <t>blog</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2650,9 +3650,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Блог</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2662,17 +3670,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>soglasie-na-obrabotku</t>
+          <t>politika-konfidencialnosti</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>/soglasienaobrabotku</t>
+          <t>/politicakonfident</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2680,9 +3688,17 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2692,13 +3708,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>spasibo</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
+          <t>soglasie-na-obrabotku</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>/soglasienaobrabotku</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Спасибо за заявку</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2706,12 +3726,54 @@
           <t>Главная</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных</t>
+        </is>
+      </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>spasibo</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за заявку</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Главная</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за заявку</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H85"/>
+  <autoFilter ref="A1:L86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4504,10 +5566,14 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>— раздел меню</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>/uslugi/</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5111,7 +6177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.5" customWidth="1" min="1" max="1"/>
@@ -6310,291 +7376,291 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Тёплый пол</t>
+          <t>Дизайн интерьера</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Монтаж тёплого пола в квартире в Москве, цена | СК Эспада</t>
+          <t>Дизайн интерьера в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Монтаж тёплого пола, водяного и электрического: расчёт мощности, укладка контура, подключение и настройка терморегулятора. Считаем по фактической площади.</t>
+          <t>Разрабатываем дизайн-проекты квартир, домов и офисов от 1 790 ₽ за м². Технический и стандартный тариф, авторский надзор. Выезд дизайнера на объект бесплатный.</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Монтаж тёплого пола</t>
+          <t>Дизайн интерьера в Москве</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера</t>
+          <t>Дизайн интерьера квартиры</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера в Москве, цена за м² | СК Эспада</t>
+          <t>Дизайн-проект квартиры в Москве от 1 790 ₽ за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Разрабатываем дизайн-проекты квартир, домов и офисов от 1 790 ₽ за м². Технический и стандартный тариф, авторский надзор. Выезд дизайнера на объект бесплатный.</t>
+          <t>Дизайн-проект квартиры: обмеры, планировочные решения, схемы электрики и сантехники, развёртки, ведомости отделки. Проект проверяем на выполнимость до сметы.</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера в Москве</t>
+          <t>Дизайн-проект квартиры</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера квартиры</t>
+          <t>Дизайн кухни</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Дизайн-проект квартиры в Москве от 1 790 ₽ за м² | СК Эспада</t>
+          <t>Дизайн кухни в Москве, разработка проекта | СК Эспада</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Дизайн-проект квартиры: обмеры, планировочные решения, схемы электрики и сантехники, развёртки, ведомости отделки. Проект проверяем на выполнимость до сметы.</t>
+          <t>Дизайн кухни: эргономика рабочего треугольника, расстановка техники, схемы подключения, освещение рабочих зон. Отдаём проект в комплекте с ведомостями.</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Дизайн-проект квартиры</t>
+          <t>Дизайн кухни</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни в Москве, разработка проекта | СК Эспада</t>
+          <t>Дизайн ванной комнаты в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни: эргономика рабочего треугольника, расстановка техники, схемы подключения, освещение рабочих зон. Отдаём проект в комплекте с ведомостями.</t>
+          <t>Дизайн ванной комнаты: раскладка плитки, развёртки стен, схемы подключения сантехники, освещение и вентиляция. Учитываем размеры помещения и вкус хозяев.</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Дизайн кухни</t>
+          <t>Дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты в Москве под ключ | СК Эспада</t>
+          <t>Дизайн спальни в Москве, проект интерьера | СК Эспада</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты: раскладка плитки, развёртки стен, схемы подключения сантехники, освещение и вентиляция. Учитываем размеры помещения и вкус хозяев.</t>
+          <t>Дизайн спальни: планировка, сценарии освещения, системы хранения, подбор отделки и текстиля. Отдаём проект со всеми схемами и ведомостью материалов.</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Дизайн ванной комнаты</t>
+          <t>Дизайн спальни</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни в Москве, проект интерьера | СК Эспада</t>
+          <t>Дизайн гостиной в Москве, проект интерьера | СК Эспада</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни: планировка, сценарии освещения, системы хранения, подбор отделки и текстиля. Отдаём проект со всеми схемами и ведомостью материалов.</t>
+          <t>Дизайн гостиной: зонирование, расстановка мебели, освещение, отделка стен и потолка. Готовим проект, по которому объект собирают без переделок на площадке.</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Дизайн спальни</t>
+          <t>Дизайн гостиной</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной в Москве, проект интерьера | СК Эспада</t>
+          <t>Дизайн детской комнаты в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной: зонирование, расстановка мебели, освещение, отделка стен и потолка. Готовим проект, по которому объект собирают без переделок на площадке.</t>
+          <t>Дизайн детской комнаты: безопасные материалы, зоны сна, игры и учёбы, освещение по нормам. Закладываем запас на взросление ребёнка. Выезд дизайнера бесплатный.</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Дизайн гостиной</t>
+          <t>Дизайн детской комнаты</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты в Москве под ключ | СК Эспада</t>
+          <t>Дизайн прихожей и коридора в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты: безопасные материалы, зоны сна, игры и учёбы, освещение по нормам. Закладываем запас на взросление ребёнка. Выезд дизайнера бесплатный.</t>
+          <t>Дизайн прихожей и коридора: системы хранения, износостойкая отделка, освещение узких пространств. Проект с развёртками и ведомостью отделочных материалов.</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Дизайн детской комнаты</t>
+          <t>Дизайн прихожей и коридора</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Дизайн квартиры-студии</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора в Москве | СК Эспада</t>
+          <t>Дизайн квартиры-студии в Москве, проект | СК Эспада</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора: системы хранения, износостойкая отделка, освещение узких пространств. Проект с развёртками и ведомостью отделочных материалов.</t>
+          <t>Дизайн студии: зонирование без стен, компактные системы хранения, продуманное освещение. Работаем с площадями от 18 м². Отдаём полный комплект чертежей.</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Дизайн прихожей и коридора</t>
+          <t>Дизайн квартиры-студии</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии в Москве, проект | СК Эспада</t>
+          <t>Дизайн интерьера офиса в Москве, проект | СК Эспада</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -6602,15 +7668,15 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Дизайн студии: зонирование без стен, компактные системы хранения, продуманное освещение. Работаем с площадями от 18 м². Отдаём полный комплект чертежей.</t>
+          <t>Дизайн офиса: планировка рабочих мест, переговорные и зоны отдыха, освещение и акустика по нормам. Готовим проект под согласование с собственником здания.</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Дизайн квартиры-студии</t>
+          <t>Дизайн интерьера офиса</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
@@ -6620,322 +7686,322 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Дизайн интерьера дома</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса в Москве, проект | СК Эспада</t>
+          <t>Дизайн интерьера дома и коттеджа в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн офиса: планировка рабочих мест, переговорные и зоны отдыха, освещение и акустика по нормам. Готовим проект под согласование с собственником здания.</t>
+          <t>Дизайн интерьера частного дома: планировка по этажам, лестницы, инженерные решения, отделка. Ведём проект от обмеров до авторского надзора на объекте.</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера офиса</t>
+          <t>Дизайн интерьера дома</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома и коттеджа в Москве | СК Эспада</t>
+          <t>Дизайн коммерческих помещений в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера частного дома: планировка по этажам, лестницы, инженерные решения, отделка. Ведём проект от обмеров до авторского надзора на объекте.</t>
+          <t>Дизайн коммерческих помещений: магазины, салоны, кафе и офисы. Учитываем сценарии посетителей, нормы и требования арендодателя. Проект с полным комплектом схем.</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Дизайн интерьера дома</t>
+          <t>Дизайн коммерческих помещений</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений в Москве | СК Эспада</t>
+          <t>Приёмка квартиры в новостройке в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений: магазины, салоны, кафе и офисы. Учитываем сценарии посетителей, нормы и требования арендодателя. Проект с полным комплектом схем.</t>
+          <t>Приёмка квартиры от застройщика с инженером: находим скрытые дефекты и составляем акт с замечаниями. Проверяем конструкции, отделку, окна и инженерные системы.</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Дизайн коммерческих помещений</t>
+          <t>Приёмка квартиры в новостройке</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в новостройке в Москве | СК Эспада</t>
+          <t>Приёмка квартиры без отделки в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры от застройщика с инженером: находим скрытые дефекты и составляем акт с замечаниями. Проверяем конструкции, отделку, окна и инженерные системы.</t>
+          <t>Приёмка квартиры без отделки: проверяем геометрию стен, стяжку, окна, вентиляцию и вводы коммуникаций. Отдаём акт с замечаниями для передачи застройщику.</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в новостройке</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки в Москве | СК Эспада</t>
+          <t>Приёмка квартиры с отделкой от застройщика | СК Эспада</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки: проверяем геометрию стен, стяжку, окна, вентиляцию и вводы коммуникаций. Отдаём акт с замечаниями для передачи застройщику.</t>
+          <t>Приёмка квартиры с чистовой отделкой: проверяем качество работ, сантехнику, электрику, двери и окна. Фиксируем дефекты в акте и помогаем добиться устранения.</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой от застройщика | СК Эспада</t>
+          <t>Приёмка квартиры в ЖК {Название} | СК Эспада</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с чистовой отделкой: проверяем качество работ, сантехнику, электрику, двери и окна. Фиксируем дефекты в акте и помогаем добиться устранения.</t>
+          <t>Приёмка квартиры в ЖК {Название}: знаем типовые дефекты этого дома и порядок работы с застройщиком. Выезд инженера с инструментом, акт в день осмотра.</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Приёмка квартиры в ЖК {Название}</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название} | СК Эспада</t>
+          <t>Комплектация квартиры материалами в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название}: знаем типовые дефекты этого дома и порядок работы с застройщиком. Выезд инженера с инструментом, акт в день осмотра.</t>
+          <t>Комплектация ремонта: подбираем черновые и чистовые материалы, мебель и технику. Считаем спецификацию, возим в шоурум, закупаем по ценам поставщиков.</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название}</t>
+          <t>Комплектация квартиры</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры материалами в Москве | СК Эспада</t>
+          <t>Услуги по ремонту и отделке квартир в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Комплектация ремонта: подбираем черновые и чистовые материалы, мебель и технику. Считаем спецификацию, возим в шоурум, закупаем по ценам поставщиков.</t>
+          <t>Все услуги СК «Эспада»: инженерные системы, отделочные и черновые работы, перепланировка. Цены, сроки и состав работ по каждому направлению.</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Комплектация квартиры</t>
+          <t>Услуги по ремонту и отделке</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Инженерные системы</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры в Москве, согласование | СК Эспада</t>
+          <t>Монтаж инженерных систем в квартире в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры с согласованием: проект, техническое заключение, подача в жилищную инспекцию, ввод изменений в документы. Ведём весь процесс сами.</t>
+          <t>Инженерные системы под ключ: электрика, сантехника, вентиляция и кондиционирование, тёплый пол, умный дом, отопление и шумоизоляция. Работаем по проекту.</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>Инженерные системы в квартире</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Тёплый пол</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен в Москве, цена | СК Эспада</t>
+          <t>Монтаж тёплого пола в квартире в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен по маякам: ровная плоскость под чистовую отделку, скорость выше ручной в разы. Считаем по фактической площади, работаем по договору.</t>
+          <t>Монтаж тёплого пола, водяного и электрического: расчёт мощности, укладка контура, подключение и настройка терморегулятора. Считаем по фактической площади.</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен</t>
+          <t>Монтаж тёплого пола</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Электромонтажные работы</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола в квартире в Москве, цена за м² | СК Эспада</t>
+          <t>Электромонтажные работы в квартире в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -6943,356 +8009,356 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Устройство стяжки пола, полусухой и мокрой, с гидроизоляцией мокрых зон. Выводим горизонт под ламинат и плитку. Считаем по площади, работаем по договору.</t>
+          <t>Электромонтаж в квартире: разводка сетей, установка щита и электроточек, замена проводки. Работаем по схеме из проекта, сдаём этап с исполнительной схемой.</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола в квартире</t>
+          <t>Электромонтажные работы в квартире</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы</t>
+          <t>Сантехнические работы</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы в квартире в Москве | СК Эспада</t>
+          <t>Сантехнические работы в квартире в Москве, цены | СК Эспада</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Электромонтаж в квартире: разводка сетей, установка щита и электроточек, замена проводки. Работаем по схеме из проекта, сдаём этап с исполнительной схемой.</t>
+          <t>Сантехника под ключ: замена труб и стояков, разводка водоснабжения и канализации, установка ванны, раковины, унитаза и полотенцесушителя. Сдаём с проверкой на протечки.</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Электромонтажные работы в квартире</t>
+          <t>Сантехнические работы в квартире</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Сантехнические работы</t>
+          <t>Шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Сантехнические работы в квартире в Москве, цены | СК Эспада</t>
+          <t>Шумоизоляция квартиры в Москве под ключ | СК Эспада</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Сантехника под ключ: замена труб и стояков, разводка водоснабжения и канализации, установка ванны, раковины, унитаза и полотенцесушителя. Сдаём с проверкой на протечки.</t>
+          <t>Шумоизоляция квартиры: стены, потолок, пол и входная дверь. Подбираем конструкцию под источник шума и считаем потерю площади заранее. Замер бесплатный.</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Сантехнические работы в квартире</t>
+          <t>Шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Установка кондиционеров</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы в квартире в Москве, цены | СК Эспада</t>
+          <t>Установка кондиционера в квартире в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж в квартире: снос перегородок по согласованию, снятие старой отделки и стяжки, вывоз мусора. Работаем с допуском от управляющей компании.</t>
+          <t>Установка и монтаж кондиционеров и сплит-систем: подбор мощности, штробление трассы до отделки, вывод дренажа, пусконаладка. Ставим в рамках ремонта и отдельно.</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы в квартире</t>
+          <t>Установка кондиционеров</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Вентиляция</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры в Москве под ключ | СК Эспада</t>
+          <t>Монтаж вентиляции в квартире в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры: стены, потолок, пол и входная дверь. Подбираем конструкцию под источник шума и считаем потерю площади заранее. Замер бесплатный.</t>
+          <t>Монтаж вентиляции в квартире: приточные установки, вытяжка в санузлах и на кухне, воздуховоды под потолком. Считаем воздухообмен по площади и числу жильцов.</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Шумоизоляция квартиры</t>
+          <t>Монтаж вентиляции в квартире</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев</t>
+          <t>Умный дом</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев в Москве, цена | СК Эспада</t>
+          <t>Умный дом в квартире под ключ в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы: шпатлёвка, покраска стен и потолков, поклейка обоев любых типов. Готовим основание под чистовое покрытие. Считаем по фактической площади.</t>
+          <t>Монтаж умного дома: сценарии освещения, управление климатом и шторами, датчики протечки и охрана. Закладываем кабельные трассы на этапе черновых работ.</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Малярные работы и поклейка обоев</t>
+          <t>Умный дом в квартире</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Отопление и радиаторы</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки в квартире в Москве, цена за м² | СК Эспада</t>
+          <t>Замена радиаторов и монтаж отопления в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Укладка керамической плитки и керамогранита: подготовка основания, гидроизоляция, раскладка по проекту, затирка швов. Считаем по фактической площади.</t>
+          <t>Замена радиаторов отопления и монтаж системы в квартире: подбор мощности батарей, перенос стояков по согласованию, опрессовка и запуск. Работаем по договору.</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Укладка плитки</t>
+          <t>Отопление и замена радиаторов</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Отделочные работы</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки в Москве под ключ, цена | СК Эспада</t>
+          <t>Отделочные работы в квартире в Москве, цены | СК Эспада</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки, матовые, сатиновые и глянцевые, с монтажом светильников и коробов. Ставим в рамках комплексного ремонта или отдельной работой.</t>
+          <t>Чистовая отделка квартиры: малярные работы и обои, укладка плитки, натяжные потолки, декоративная штукатурка. Считаем по фактической площади, смета в договоре.</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Натяжные потолки</t>
+          <t>Отделочные работы в квартире</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Малярные работы и поклейка обоев</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен в квартире в Москве, цена | СК Эспада</t>
+          <t>Малярные работы и поклейка обоев в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен под чистовую отделку: штукатурка по маякам, шпатлёвка, контроль плоскости правилом. Считаем по фактической площади, смета в договоре.</t>
+          <t>Малярные работы: шпатлёвка, покраска стен и потолков, поклейка обоев любых типов. Готовим основание под чистовое покрытие. Считаем по фактической площади.</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Малярные работы и поклейка обоев</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
+          <t>Укладка плитки</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Монтаж инженерных систем в квартире в Москве | СК Эспада</t>
+          <t>Укладка плитки в квартире в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы под ключ: электрика, сантехника, вентиляция и кондиционирование, тёплый пол, умный дом, отопление и шумоизоляция. Работаем по проекту.</t>
+          <t>Укладка керамической плитки и керамогранита: подготовка основания, гидроизоляция, раскладка по проекту, затирка швов. Считаем по фактической площади.</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы в квартире</t>
+          <t>Укладка плитки</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Установка кондиционеров</t>
+          <t>Натяжные потолки</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Установка кондиционера в квартире в Москве, цена | СК Эспада</t>
+          <t>Натяжные потолки в Москве под ключ, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Установка и монтаж кондиционеров и сплит-систем: подбор мощности, штробление трассы до отделки, вывод дренажа, пусконаладка. Ставим в рамках ремонта и отдельно.</t>
+          <t>Натяжные потолки, матовые, сатиновые и глянцевые, с монтажом светильников и коробов. Ставим в рамках комплексного ремонта или отдельной работой.</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Установка кондиционеров</t>
+          <t>Натяжные потолки</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Вентиляция</t>
+          <t>Декоративная штукатурка</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Монтаж вентиляции в квартире в Москве, цена | СК Эспада</t>
+          <t>Декоративная штукатурка стен в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Монтаж вентиляции в квартире: приточные установки, вытяжка в санузлах и на кухне, воздуховоды под потолком. Считаем воздухообмен по площади и числу жильцов.</t>
+          <t>Нанесение декоративной штукатурки: венецианская, фактурная, под бетон и микроцемент. Готовим основание, делаем выкрасы до старта. Считаем по фактической площади.</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Монтаж вентиляции в квартире</t>
+          <t>Декоративная штукатурка стен</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
@@ -7302,74 +8368,74 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Умный дом</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Умный дом в квартире под ключ в Москве, цена | СК Эспада</t>
+          <t>Демонтаж и черновые работы в квартире в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Монтаж умного дома: сценарии освещения, управление климатом и шторами, датчики протечки и охрана. Закладываем кабельные трассы на этапе черновых работ.</t>
+          <t>Черновой этап ремонта: демонтаж старой отделки и перегородок, стяжка пола, механизированная штукатурка, выравнивание стен. Сдаём этап с исполнительной документацией.</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Умный дом в квартире</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Отопление и радиаторы</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Замена радиаторов и монтаж отопления в Москве | СК Эспада</t>
+          <t>Механизированная штукатурка стен в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Замена радиаторов отопления и монтаж системы в квартире: подбор мощности батарей, перенос стояков по согласованию, опрессовка и запуск. Работаем по договору.</t>
+          <t>Механизированная штукатурка стен по маякам: ровная плоскость под чистовую отделку, скорость выше ручной в разы. Считаем по фактической площади, работаем по договору.</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Отопление и замена радиаторов</t>
+          <t>Механизированная штукатурка стен</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы в квартире в Москве, цены | СК Эспада</t>
+          <t>Стяжка пола в квартире в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -7377,286 +8443,286 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Чистовая отделка квартиры: малярные работы и обои, укладка плитки, натяжные потолки, декоративная штукатурка. Считаем по фактической площади, смета в договоре.</t>
+          <t>Устройство стяжки пола, полусухой и мокрой, с гидроизоляцией мокрых зон. Выводим горизонт под ламинат и плитку. Считаем по площади, работаем по договору.</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы в квартире</t>
+          <t>Стяжка пола в квартире</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Декоративная штукатурка</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Декоративная штукатурка стен в Москве, цена за м² | СК Эспада</t>
+          <t>Демонтажные работы в квартире в Москве, цены | СК Эспада</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Нанесение декоративной штукатурки: венецианская, фактурная, под бетон и микроцемент. Готовим основание, делаем выкрасы до старта. Считаем по фактической площади.</t>
+          <t>Демонтаж в квартире: снос перегородок по согласованию, снятие старой отделки и стяжки, вывоз мусора. Работаем с допуском от управляющей компании.</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Декоративная штукатурка стен</t>
+          <t>Демонтажные работы в квартире</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Выравнивание стен</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы в квартире в Москве | СК Эспада</t>
+          <t>Выравнивание стен в квартире в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Черновой этап ремонта: демонтаж старой отделки и перегородок, стяжка пола, механизированная штукатурка, выравнивание стен. Сдаём этап с исполнительной документацией.</t>
+          <t>Выравнивание стен под чистовую отделку: штукатурка по маякам, шпатлёвка, контроль плоскости правилом. Считаем по фактической площади, смета в договоре.</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Выравнивание стен</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Портфолио ремонтов квартир в Москве, фото работ | СК Эспада</t>
+          <t>Перепланировка квартиры в Москве, согласование | СК Эспада</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Наши работы: фото готовых квартир, площадь, сроки и состав работ по каждому объекту. Фильтры по типу ремонта, числу комнат и жилому комплексу.</t>
+          <t>Перепланировка квартиры с согласованием: проект, техническое заключение, подача в жилищную инспекцию, ввод изменений в документы. Ведём весь процесс сами.</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Портфолио выполненных работ</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Отзывы о ремонте квартир от клиентов | СК Эспада</t>
+          <t>Портфолио ремонтов квартир в Москве, фото работ | СК Эспада</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Отзывы клиентов о ремонте и дизайне квартир: что заказывали, как шли работы, что получилось. Каждый отзыв можно проверить, к нему приложены фото объекта.</t>
+          <t>Наши работы: фото готовых квартир, площадь, сроки и состав работ по каждому объекту. Фильтры по типу ремонта, числу комнат и жилому комплексу.</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Отзывы клиентов</t>
+          <t>Портфолио выполненных работ</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы о ремонте квартир | СК Эспада</t>
+          <t>Отзывы о ремонте квартир от клиентов | СК Эспада</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Отвечаем на вопросы о сроках, смете, договоре, оплате и гарантии. Что входит в ремонт под ключ, как считается стоимость и что делать при изменениях в проекте.</t>
+          <t>Отзывы клиентов о ремонте и дизайне квартир: что заказывали, как шли работы, что получилось. Каждый отзыв можно проверить, к нему приложены фото объекта.</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Отзывы клиентов</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>О компании СК Эспада, ремонт квартир в Москве</t>
+          <t>Вопросы и ответы о ремонте квартир | СК Эспада</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>СК «Эспада» делает ремонт и дизайн квартир в Москве и области. Команда, гарантии, лицензии и реквизиты. Работаем по договору с фиксированной сметой.</t>
+          <t>Отвечаем на вопросы о сроках, смете, договоре, оплате и гарантии. Что входит в ремонт под ключ, как считается стоимость и что делать при изменениях в проекте.</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Контакты СК Эспада в Москве, адрес и телефон</t>
+          <t>О компании СК Эспада, ремонт квартир в Москве</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Офис в Москве, улица Дегунинская, дом 1, корпус 2. Телефон +7 (993) 891-40-64, почта sk-espada@rambler.ru. Схема проезда и форма обратной связи.</t>
+          <t>СК «Эспада» делает ремонт и дизайн квартир в Москве и области. Команда, гарантии, лицензии и реквизиты. Работаем по договору с фиксированной сметой.</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа для дизайнеров и агентов | СК Эспада</t>
+          <t>Контакты СК Эспада в Москве, адрес и телефон</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам: стабильный поток клиентов, прозрачные условия и быстрые выплаты. Работаем с дизайнерами, риелторами и смежными подрядчиками. Оставьте заявку.</t>
+          <t>Офис в Москве, улица Дегунинская, дом 1, корпус 2. Телефон +7 (993) 891-40-64, почта sk-espada@rambler.ru. Схема проезда и форма обратной связи.</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Блог о ремонте и дизайне квартир | СК Эспада</t>
+          <t>Партнёрская программа для дизайнеров и агентов | СК Эспада</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Статьи о ремонте и дизайне: как считать бюджет, что выбрать из материалов, с чего начинать работы и как контролировать подрядчика. Разборы от инженеров.</t>
+          <t>Партнёрам: стабильный поток клиентов, прозрачные условия и быстрые выплаты. Работаем с дизайнерами, риелторами и смежными подрядчиками. Оставьте заявку.</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -7664,61 +8730,61 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Блог о ремонте и дизайне</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности | СК Эспада</t>
+          <t>Блог о ремонте и дизайне квартир | СК Эспада</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Как СК «Эспада» обрабатывает и защищает персональные данные посетителей сайта: какие данные собираются, для чего используются и как их удалить.</t>
+          <t>Статьи о ремонте и дизайне: как считать бюджет, что выбрать из материалов, с чего начинать работы и как контролировать подрядчика. Разборы от инженеров.</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Блог о ремонте и дизайне</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных | СК Эспада</t>
+          <t>Политика конфиденциальности | СК Эспада</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Текст согласия, которое посетитель даёт при отправке заявки на сайте: перечень данных, цели обработки, срок хранения и порядок отзыва согласия.</t>
+          <t>Как СК «Эспада» обрабатывает и защищает персональные данные посетителей сайта: какие данные собираются, для чего используются и как их удалить.</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -7726,46 +8792,77 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>Согласие на обработку персональных данных</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных | СК Эспада</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Текст согласия, которое посетитель даёт при отправке заявки на сайте: перечень данных, цели обработки, срок хранения и порядок отзыва согласия.</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Согласие на обработку персональных данных</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
           <t>Спасибо за заявку</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Заявка отправлена | СК Эспада</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C86" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Заявка принята. Инженер перезвонит в течение рабочего дня, согласует время выезда на замер и ответит на вопросы по смете.</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E86" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Заявка отправлена</t>
         </is>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="G86" s="2" t="n">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85"/>
+  <autoFilter ref="A1:G86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7776,7 +8873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11708,12 +12805,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>/demontazh-i-chernovye-raboty/</t>
+          <t>/uslugi/</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -11754,17 +12851,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/demontazh-i-chernovye-raboty/</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -11787,29 +12884,25 @@
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Поисковой роли нет</t>
+          <t>Спроса не найдено</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Хочу такой же ремонт</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
           <t>Бесплатный расчёт сметы</t>
         </is>
       </c>
+      <c r="L76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -11854,12 +12947,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>/faq/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -11904,12 +12997,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>/o-kompanii/</t>
+          <t>/faq/</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -11954,12 +13047,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>/kontakty/</t>
+          <t>/o-kompanii/</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -12004,12 +13097,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>/partners/</t>
+          <t>/kontakty/</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -12019,7 +13112,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
@@ -12037,25 +13130,29 @@
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Поисковой роли нет</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Стать партнёром</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr"/>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/partners/</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12065,7 +13162,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -12083,34 +13180,30 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Поисковой роли нет</t>
+          <t>Спроса не найдено</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Хочу такой же ремонт</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>Бесплатный расчёт сметы</t>
-        </is>
-      </c>
+          <t>Стать партнёром</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>/politika-konfidencialnosti/</t>
+          <t>/blog/</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Служебные</t>
+          <t>Доверие</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -12136,18 +13229,26 @@
           <t>Поисковой роли нет</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>/soglasie-na-obrabotku/</t>
+          <t>/politika-konfidencialnosti/</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12184,12 +13285,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>/spasibo/</t>
+          <t>/soglasie-na-obrabotku/</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Спасибо за заявку</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12223,8 +13324,50 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>/spasibo/</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за заявку</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Служебные</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L85"/>
+  <autoFilter ref="A1:L86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14297,10 +15440,14 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>— раздел меню</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
+          <t>Услуги</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>/uslugi/</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -15002,7 +16149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16137,11 +17284,11 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Тёплый пол</t>
+          <t xml:space="preserve">        Тёплый пол</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -16665,11 +17812,11 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t xml:space="preserve">    Перепланировка квартиры</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -16677,7 +17824,11 @@
           <t>pereplanirovka-kvartiry</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>uslugi</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>/pereplanirovka-kvartiry/</t>
@@ -16691,11 +17842,11 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Механизированная штукатурка</t>
+          <t xml:space="preserve">        Механизированная штукатурка</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -16721,11 +17872,11 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Стяжка пола</t>
+          <t xml:space="preserve">        Стяжка пола</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -16751,11 +17902,11 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Электромонтажные работы</t>
+          <t xml:space="preserve">        Электромонтажные работы</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -16781,11 +17932,11 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Сантехнические работы</t>
+          <t xml:space="preserve">        Сантехнические работы</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -16811,11 +17962,11 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Демонтажные работы</t>
+          <t xml:space="preserve">        Демонтажные работы</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -16841,11 +17992,11 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Шумоизоляция квартиры</t>
+          <t xml:space="preserve">        Шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -16871,11 +18022,11 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Малярные работы и поклейка обоев</t>
+          <t xml:space="preserve">        Малярные работы и поклейка обоев</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -16901,11 +18052,11 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Укладка плитки</t>
+          <t xml:space="preserve">        Укладка плитки</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -16931,11 +18082,11 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Натяжные потолки</t>
+          <t xml:space="preserve">        Натяжные потолки</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -16961,11 +18112,11 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Выравнивание стен</t>
+          <t xml:space="preserve">        Выравнивание стен</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -16995,18 +18146,18 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>inzhenernye-sistemy</t>
+          <t>uslugi</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/uslugi/</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -17021,22 +18172,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Установка кондиционеров</t>
+          <t xml:space="preserve">    Инженерные системы</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>ustanovka-konditsionerov</t>
+          <t>inzhenernye-sistemy</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>inzhenernye-sistemy</t>
+          <t>uslugi</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -17047,16 +18198,16 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Вентиляция</t>
+          <t xml:space="preserve">        Установка кондиционеров</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>ventilyatsiya</t>
+          <t>ustanovka-konditsionerov</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -17066,7 +18217,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -17077,16 +18228,16 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Умный дом</t>
+          <t xml:space="preserve">        Вентиляция</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>umnyj-dom</t>
+          <t>ventilyatsiya</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -17096,7 +18247,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -17107,16 +18258,16 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Отопление и радиаторы</t>
+          <t xml:space="preserve">        Умный дом</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>otoplenie-i-radiatory</t>
+          <t>umnyj-dom</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -17126,7 +18277,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -17137,22 +18288,26 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
+          <t xml:space="preserve">        Отопление и радиаторы</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>otdelochnye-raboty</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>otoplenie-i-radiatory</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>inzhenernye-sistemy</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>/otdelochnye-raboty/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -17167,22 +18322,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Декоративная штукатурка</t>
+          <t xml:space="preserve">    Отделочные работы</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>dekorativnaya-shtukaturka</t>
+          <t>otdelochnye-raboty</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>otdelochnye-raboty</t>
+          <t>uslugi</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/otdelochnye-raboty/</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -17193,22 +18348,26 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t xml:space="preserve">        Декоративная штукатурка</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>demontazh-i-chernovye-raboty</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>dekorativnaya-shtukaturka</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>otdelochnye-raboty</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>/demontazh-i-chernovye-raboty/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -17219,22 +18378,26 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t xml:space="preserve">    Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>portfolio</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+          <t>demontazh-i-chernovye-raboty</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>uslugi</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/demontazh-i-chernovye-raboty/</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -17249,18 +18412,18 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>otzyvy</t>
+          <t>portfolio</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -17275,18 +18438,18 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>faq</t>
+          <t>otzyvy</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>/faq/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -17301,18 +18464,18 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>o-kompanii</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>/o-kompanii/</t>
+          <t>/faq/</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -17327,18 +18490,18 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>kontakty</t>
+          <t>o-kompanii</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>/kontakty/</t>
+          <t>/o-kompanii/</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -17353,23 +18516,23 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>kontakty</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>/partners/</t>
+          <t>/kontakty/</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
     </row>
@@ -17379,23 +18542,23 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>blog</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/partners/</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
     </row>
@@ -17405,18 +18568,18 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>politika-konfidencialnosti</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>/politika-konfidencialnosti/</t>
+          <t>/blog/</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -17431,18 +18594,18 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>soglasie-na-obrabotku</t>
+          <t>politika-konfidencialnosti</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>/soglasie-na-obrabotku/</t>
+          <t>/politika-konfidencialnosti/</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -17457,28 +18620,54 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Спасибо за заявку</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>spasibo</t>
+          <t>soglasie-na-obrabotku</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
+          <t>/soglasie-na-obrabotku/</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Необходимо создать</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Спасибо за заявку</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>spasibo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>/spasibo/</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Необходимо создать</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F85"/>
+  <autoFilter ref="A1:F86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17489,7 +18678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -22054,17 +23243,17 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>перепланировка квартиры в москве согласование</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -22084,12 +23273,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -22109,12 +23298,12 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -22134,12 +23323,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -22154,17 +23343,17 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -22184,12 +23373,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -22209,12 +23398,12 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -22234,12 +23423,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -22254,17 +23443,17 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>декоративная штукатурка</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -22284,12 +23473,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>укладка плитки цена за м2 в москве и московской</t>
+          <t>декоративная штукатурка</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -22309,12 +23498,12 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>материалы натяжных потолков</t>
+          <t>укладка плитки цена за м2 в москве и московской</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -22329,17 +23518,17 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>сухая стяжка пола кнауф</t>
+          <t>материалы натяжных потолков</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -22359,12 +23548,12 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>выравнивание стен по маякам</t>
+          <t>сухая стяжка пола кнауф</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -22379,17 +23568,17 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>малярные работы</t>
+          <t>выравнивание стен по маякам</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -22409,12 +23598,12 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>укладка плитки цена за м2 в москве и московской</t>
+          <t>малярные работы</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -22429,17 +23618,17 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>укладка плитки цена за м2 в москве и московской</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -22459,12 +23648,12 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -22484,12 +23673,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -22509,12 +23698,12 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -22529,17 +23718,17 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>вентиляция в квартире</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -22559,12 +23748,12 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>вентиляция в квартире</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -22584,12 +23773,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>для теплого пола подложка</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -22609,12 +23798,12 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>электромонтаж в квартире</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -22629,17 +23818,17 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>приемка квартиры пик с отделкой</t>
+          <t>электромонтаж в квартире</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -22654,17 +23843,17 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-v-zhk-shablon/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>инженерные системы</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -22679,17 +23868,17 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
           <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
-        </is>
-      </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>приемка квартиры в новостройке без отделки</t>
+          <t>приемка квартиры пик с отделкой</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -22704,7 +23893,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -22729,7 +23918,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-v-zhk-shablon/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -22754,17 +23943,17 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
           <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
-        </is>
-      </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>приемка квартиры пик с отделкой</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -22779,17 +23968,17 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>ремонт однокомнатной квартиры</t>
+          <t>приемка квартиры в новостройке без отделки</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -22804,17 +23993,17 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>приемка квартиры пик с отделкой</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -22834,12 +24023,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>ремонт кухни</t>
+          <t>ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -22859,12 +24048,12 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -22879,17 +24068,17 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>ремонт кухни</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -22904,17 +24093,17 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -22934,12 +24123,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -22959,12 +24148,12 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -22979,17 +24168,17 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -23004,17 +24193,17 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -23034,12 +24223,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>ремонт в 2х комнатной квартире панельного дома</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -23059,12 +24248,12 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>ремонт после пожара</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -23079,17 +24268,17 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -23104,17 +24293,17 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>ремонт после пожара</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -23134,12 +24323,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -23159,12 +24348,12 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -23179,17 +24368,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -23204,17 +24393,17 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -23234,12 +24423,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -23259,12 +24448,12 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -23279,17 +24468,17 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -23304,17 +24493,17 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -23334,12 +24523,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -23359,12 +24548,12 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -23379,17 +24568,17 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -23404,17 +24593,17 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -23434,12 +24623,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -23459,12 +24648,12 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -23479,17 +24668,17 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -23504,17 +24693,17 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -23534,12 +24723,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -23559,12 +24748,12 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -23579,17 +24768,17 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>/tseny-na-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -23604,17 +24793,17 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>ремонт ванной комнаты</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -23634,12 +24823,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/tseny-na-remont-kvartir/</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>сколько стоит ремонт квартиры</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -23659,12 +24848,12 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -23679,17 +24868,17 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -23704,17 +24893,17 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -23734,12 +24923,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -23759,12 +24948,12 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -23779,17 +24968,17 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -23804,17 +24993,17 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>ремонт в 2х комнатной квартире панельного дома</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -23829,17 +25018,17 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -23854,17 +25043,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -23884,12 +25073,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -23909,12 +25098,12 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -23929,17 +25118,17 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>ремонт кухни</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -23954,17 +25143,17 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -23984,12 +25173,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>ремонт кухни</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -24009,12 +25198,12 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -24029,17 +25218,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -24054,17 +25243,17 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -24084,12 +25273,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -24109,12 +25298,12 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -24129,17 +25318,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -24154,17 +25343,17 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -24184,12 +25373,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -24209,12 +25398,12 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -24229,17 +25418,17 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -24254,17 +25443,17 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -24284,12 +25473,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -24309,12 +25498,12 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -24329,17 +25518,17 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -24354,17 +25543,17 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -24384,12 +25573,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -24409,12 +25598,12 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -24429,17 +25618,17 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -24454,17 +25643,17 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -24484,12 +25673,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>ремонт после пожара</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -24504,17 +25693,17 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -24529,17 +25718,17 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>ремонт после пожара</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -24559,12 +25748,12 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -24584,12 +25773,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -24604,17 +25793,17 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -24629,17 +25818,17 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -24659,12 +25848,12 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -24684,12 +25873,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -24704,17 +25893,17 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>/tseny-na-remont-kvartir/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -24729,17 +25918,17 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>ремонт однокомнатной квартиры</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -24759,12 +25948,12 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/tseny-na-remont-kvartir/</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>сколько стоит ремонт квартиры</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -24779,17 +25968,17 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>для теплого пола подложка</t>
+          <t>ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -24804,17 +25993,17 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>электромонтаж в квартире</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -24829,17 +26018,17 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>установка кондиционера</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -24854,17 +26043,17 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>вентиляция в квартире</t>
+          <t>электромонтаж в квартире</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -24884,12 +26073,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>замена радиаторов отопления</t>
+          <t>установка кондиционера</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -24909,12 +26098,12 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>для теплого пола подложка</t>
+          <t>вентиляция в квартире</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -24929,17 +26118,17 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>штукатурка механизированная</t>
+          <t>замена радиаторов отопления</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -24954,17 +26143,17 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>выравнивание стен по маякам</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -24984,12 +26173,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>демонтажные работы</t>
+          <t>штукатурка механизированная</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -25004,17 +26193,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>/tseny-na-remont-kvartir/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>ремонт ванной комнаты</t>
+          <t>выравнивание стен по маякам</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -25029,17 +26218,17 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>/tseny-na-remont-kvartir/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>ремонт однокомнатной квартиры</t>
+          <t>демонтажные работы</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
@@ -25054,17 +26243,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/tseny-na-remont-kvartir/</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
@@ -25079,17 +26268,17 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/tseny-na-remont-kvartir/</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>замена радиаторов отопления</t>
+          <t>ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -25109,12 +26298,12 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>электромонтаж в квартире</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -25134,12 +26323,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>замена труб в ванной</t>
+          <t>замена радиаторов отопления</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -25154,17 +26343,17 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>декоративная штукатурка</t>
+          <t>электромонтаж в квартире</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -25179,17 +26368,17 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>малярные работы</t>
+          <t>замена труб в ванной</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -25209,12 +26398,12 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>материалы натяжных потолков</t>
+          <t>декоративная штукатурка</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
@@ -25229,17 +26418,17 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>установка кондиционера</t>
+          <t>малярные работы</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
@@ -25254,17 +26443,17 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>вентиляция в квартире</t>
+          <t>материалы натяжных потолков</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
@@ -25279,17 +26468,17 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
+          <t>/umnyj-dom/</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
           <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>/umnyj-dom/</t>
-        </is>
-      </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>умный дом</t>
+          <t>установка кондиционера</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -25304,7 +26493,7 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -25334,12 +26523,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>умный дом</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -25354,17 +26543,17 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
+          <t>/ustanovka-konditsionerov/</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
           <t>/ventilyatsiya/</t>
         </is>
       </c>
-      <c r="B315" s="2" t="inlineStr">
-        <is>
-          <t>/umnyj-dom/</t>
-        </is>
-      </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>умный дом</t>
+          <t>вентиляция в квартире</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
@@ -25379,17 +26568,17 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>установка кондиционера</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -25409,12 +26598,12 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>умный дом</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
@@ -25434,12 +26623,12 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>замена радиаторов отопления</t>
+          <t>установка кондиционера</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -25454,17 +26643,17 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>штукатурка механизированная</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -25479,17 +26668,17 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>сухая стяжка пола кнауф</t>
+          <t>замена радиаторов отопления</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -25509,12 +26698,12 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>демонтажные работы</t>
+          <t>штукатурка механизированная</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -25529,22 +26718,22 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>сухая стяжка пола кнауф</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Услуга в пиллар</t>
+          <t>Между соседями</t>
         </is>
       </c>
       <c r="E322" s="2" t="n">
@@ -25554,22 +26743,22 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
+          <t>/vyravnivanie-sten/</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
           <t>/demontazhnye-raboty/</t>
         </is>
       </c>
-      <c r="B323" s="2" t="inlineStr">
-        <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
-        </is>
-      </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>демонтажные работы</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Услуга в пиллар</t>
+          <t>Между соседями</t>
         </is>
       </c>
       <c r="E323" s="2" t="n">
@@ -25579,7 +26768,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -25604,7 +26793,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -25629,7 +26818,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -25654,7 +26843,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -25679,7 +26868,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -25704,7 +26893,7 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -25729,7 +26918,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -25754,7 +26943,7 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -25779,7 +26968,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -25804,7 +26993,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -25829,7 +27018,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -25854,7 +27043,7 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -25879,7 +27068,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -25904,7 +27093,7 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -25929,7 +27118,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -25954,7 +27143,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -25979,7 +27168,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -26004,7 +27193,7 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -26019,36 +27208,36 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Доверие в пиллар</t>
+          <t>Услуга в пиллар</t>
         </is>
       </c>
       <c r="E341" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>дизайн интерьера</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Доверие в пиллар</t>
+          <t>Услуга в пиллар</t>
         </is>
       </c>
       <c r="E342" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -26059,12 +27248,12 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>приемка квартир москва в новостройках</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
@@ -26079,17 +27268,17 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>дизайн интерьера</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -26104,17 +27293,17 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>дизайн интерьера</t>
+          <t>приемка квартир москва в новостройках</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
@@ -26134,12 +27323,12 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>приемка квартир москва в новостройках</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -26154,22 +27343,22 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>/blog/chernovoj-remont-kvartiry/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, черновой ремонт квартиры</t>
+          <t>дизайн интерьера</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Коммерция в блог</t>
+          <t>Доверие в пиллар</t>
         </is>
       </c>
       <c r="E347" s="2" t="n">
@@ -26179,22 +27368,22 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>/blog/chistovaya-otdelka-kvartiry/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, чистовая отделка квартиры</t>
+          <t>приемка квартир москва в новостройках</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Коммерция в блог</t>
+          <t>Доверие в пиллар</t>
         </is>
       </c>
       <c r="E348" s="2" t="n">
@@ -26204,17 +27393,17 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>/blog/dekorativnaya-shtukaturka/</t>
+          <t>/blog/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, декоративная штукатурка</t>
+          <t>Статьи о том, черновой ремонт квартиры</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -26229,17 +27418,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-detskoj-komnaty/</t>
+          <t>/blog/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн детской комнаты</t>
+          <t>Статьи о том, чистовая отделка квартиры</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -26254,17 +27443,17 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-interera-doma/</t>
+          <t>/blog/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн интерьера дома</t>
+          <t>Статьи о том, декоративная штукатурка</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -26279,17 +27468,17 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-interera-kvartiry/</t>
+          <t>/blog/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн интерьера квартиры</t>
+          <t>Статьи о том, дизайн детской комнаты</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -26304,17 +27493,17 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-interera/</t>
+          <t>/blog/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн интерьера</t>
+          <t>Статьи о том, дизайн интерьера дома</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -26329,17 +27518,17 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-kuhni/</t>
+          <t>/blog/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн кухни</t>
+          <t>Статьи о том, дизайн интерьера квартиры</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -26354,17 +27543,17 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-spalni/</t>
+          <t>/blog/dizajn-interera/</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн спальни</t>
+          <t>Статьи о том, дизайн интерьера</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -26379,17 +27568,17 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-vannoj-komnaty/</t>
+          <t>/blog/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн ванной комнаты</t>
+          <t>Статьи о том, дизайн кухни</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -26404,17 +27593,17 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajnerskij-remont-kvartiry/</t>
+          <t>/blog/dizajn-spalni/</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайнерский ремонт квартиры</t>
+          <t>Статьи о том, дизайн спальни</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
@@ -26429,17 +27618,17 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>/blog/elektromontazhnye-raboty/</t>
+          <t>/blog/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, электромонтажные работы</t>
+          <t>Статьи о том, дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -26454,17 +27643,17 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>/blog/evroremont-kvartiry/</t>
+          <t>/blog/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, евроремонт квартиры</t>
+          <t>Статьи о том, дизайнерский ремонт квартиры</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -26479,17 +27668,17 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>/blog/kapitalnyj-remont-kvartiry/</t>
+          <t>/blog/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, капитальный ремонт квартиры</t>
+          <t>Статьи о том, электромонтажные работы</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -26504,17 +27693,17 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>/blog/komplektatsiya-kvartiry/</t>
+          <t>/blog/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, комплектация квартиры</t>
+          <t>Статьи о том, евроремонт квартиры</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -26529,17 +27718,17 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>/blog/kosmeticheskij-remont-kvartiry/</t>
+          <t>/blog/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, косметический ремонт квартиры</t>
+          <t>Статьи о том, капитальный ремонт квартиры</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -26554,17 +27743,17 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>/blog/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/blog/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, малярные работы и поклейка обоев</t>
+          <t>Статьи о том, комплектация квартиры</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -26579,17 +27768,17 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>/blog/natyazhnye-potolki/</t>
+          <t>/blog/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, натяжные потолки</t>
+          <t>Статьи о том, косметический ремонт квартиры</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -26604,17 +27793,17 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/blog/nedorogoj-remont-kvartir/</t>
+          <t>/blog/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, недорогой ремонт квартир</t>
+          <t>Статьи о том, малярные работы и поклейка обоев</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -26629,17 +27818,17 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>/blog/otoplenie-i-radiatory/</t>
+          <t>/blog/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, отопление и радиаторы</t>
+          <t>Статьи о том, натяжные потолки</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -26654,17 +27843,17 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>/blog/pereplanirovka-kvartiry/</t>
+          <t>/blog/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, перепланировка квартиры</t>
+          <t>Статьи о том, недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -26679,17 +27868,17 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/blog/priyomka-kvartir-v-novostrojke/</t>
+          <t>/blog/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, приёмка квартир в новостройке</t>
+          <t>Статьи о том, отопление и радиаторы</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -26704,17 +27893,17 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/blog/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/blog/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, приёмка квартиры без отделки</t>
+          <t>Статьи о том, перепланировка квартиры</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
@@ -26729,17 +27918,17 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/blog/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт двухкомнатной квартиры</t>
+          <t>Статьи о том, приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -26754,17 +27943,17 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-gostinoj/</t>
+          <t>/blog/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт гостиной</t>
+          <t>Статьи о том, приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -26779,17 +27968,17 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kuhni/</t>
+          <t>/blog/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт кухни</t>
+          <t>Статьи о том, ремонт двухкомнатной квартиры</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -26804,17 +27993,17 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kvartir-po-stilyu/</t>
+          <t>/blog/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт квартир по стилю</t>
+          <t>Статьи о том, ремонт гостиной</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -26829,17 +28018,17 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kvartiry-na-vtorichke/</t>
+          <t>/blog/remont-kuhni/</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт квартиры на вторичке</t>
+          <t>Статьи о том, ремонт кухни</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -26854,17 +28043,17 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kvartiry-v-novostrojke/</t>
+          <t>/blog/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт квартиры в новостройке</t>
+          <t>Статьи о том, ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -26879,17 +28068,17 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/blog/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт однокомнатной квартиры</t>
+          <t>Статьи о том, ремонт квартиры на вторичке</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
@@ -26904,17 +28093,17 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-pod-sdachu-v-arendu/</t>
+          <t>/blog/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт под сдачу в аренду</t>
+          <t>Статьи о том, ремонт квартиры в новостройке</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
@@ -26929,17 +28118,17 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-prihozhej-i-koridora/</t>
+          <t>/blog/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт прихожей и коридора</t>
+          <t>Статьи о том, ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
@@ -26954,17 +28143,17 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-sanuzla/</t>
+          <t>/blog/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт санузла</t>
+          <t>Статьи о том, ремонт под сдачу в аренду</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
@@ -26979,17 +28168,17 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-spalni/</t>
+          <t>/blog/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт спальни</t>
+          <t>Статьи о том, ремонт прихожей и коридора</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
@@ -27004,17 +28193,17 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/blog/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт трёхкомнатной квартиры</t>
+          <t>Статьи о том, ремонт санузла</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
@@ -27029,17 +28218,17 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-tualeta/</t>
+          <t>/blog/remont-spalni/</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт туалета</t>
+          <t>Статьи о том, ремонт спальни</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
@@ -27054,17 +28243,17 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-v-hrushchyovke/</t>
+          <t>/blog/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт в хрущёвке</t>
+          <t>Статьи о том, ремонт трёхкомнатной квартиры</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
@@ -27079,17 +28268,17 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-v-panelnom-dome/</t>
+          <t>/blog/remont-tualeta/</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт в панельном доме</t>
+          <t>Статьи о том, ремонт туалета</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -27104,17 +28293,17 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-vannoj-komnaty/</t>
+          <t>/blog/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт ванной комнаты</t>
+          <t>Статьи о том, ремонт в хрущёвке</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -27129,17 +28318,17 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/blog/santehnicheskie-raboty/</t>
+          <t>/blog/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, сантехнические работы</t>
+          <t>Статьи о том, ремонт в панельном доме</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -27154,17 +28343,17 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>/blog/shumoizolyatsiya-kvartiry/</t>
+          <t>/blog/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, шумоизоляция квартиры</t>
+          <t>Статьи о том, ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -27179,17 +28368,17 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/blog/styazhka-pola/</t>
+          <t>/blog/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, стяжка пола</t>
+          <t>Статьи о том, сантехнические работы</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -27204,17 +28393,17 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>/tseny-na-remont-kvartir/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/blog/tseny-na-remont-kvartir/</t>
+          <t>/blog/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, цены на ремонт квартир</t>
+          <t>Статьи о том, шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
@@ -27229,17 +28418,17 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>/blog/tyoplyj-pol/</t>
+          <t>/blog/styazhka-pola/</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, тёплый пол</t>
+          <t>Статьи о том, стяжка пола</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -27254,17 +28443,17 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/tseny-na-remont-kvartir/</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>/blog/ukladka-plitki/</t>
+          <t>/blog/tseny-na-remont-kvartir/</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, укладка плитки</t>
+          <t>Статьи о том, цены на ремонт квартир</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
@@ -27279,17 +28468,17 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>/blog/vyravnivanie-sten/</t>
+          <t>/blog/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, выравнивание стен</t>
+          <t>Статьи о том, тёплый пол</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -27304,22 +28493,22 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/blog/ukladka-plitki/</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Статьи о том, укладка плитки</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в доверие</t>
+          <t>Коммерция в блог</t>
         </is>
       </c>
       <c r="E393" s="2" t="n">
@@ -27329,22 +28518,22 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/blog/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Статьи о том, выравнивание стен</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в доверие</t>
+          <t>Коммерция в блог</t>
         </is>
       </c>
       <c r="E394" s="2" t="n">
@@ -27354,7 +28543,7 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -27379,7 +28568,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -27404,7 +28593,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -27429,7 +28618,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -27451,8 +28640,58 @@
         <v>3</v>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kvartir-pod-klyuch/</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kvartir-pod-klyuch/</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E398"/>
+  <autoFilter ref="A1:E400"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
+++ b/other/Семантика и структура/СТРУКТУРА САЙТА _ СК ЭСПАДА _ SEO VICTORY.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спрос по страницам'!$A$1:$L$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Шапка сайта'!$A$1:$F$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Иерархия в админке'!$A$1:$F$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Перелинковка'!$A$1:$E$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Перелинковка'!$A$1:$E$408</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2963,22 +2963,18 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Редирект</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>priyomka-kvartir-v-novostrojke</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>/priemka</t>
-        </is>
-      </c>
+          <t>demontazh-i-chernovye-raboty</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2993,7 +2989,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3010,18 +3006,18 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>priyomka-kvartiry-bez-otdelki</t>
+          <t>mehanizirovannaya-shtukaturka</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -3031,12 +3027,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3052,18 +3048,18 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>priyomka-kvartiry-s-otdelkoj</t>
+          <t>styazhka-pola</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3073,12 +3069,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3094,18 +3090,18 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>priyomka-v-zhk-shablon</t>
+          <t>demontazhnye-raboty</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3115,12 +3111,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3136,31 +3132,35 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>demontazh-i-chernovye-raboty</t>
+          <t>vyravnivanie-sten</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>Демонтаж и черновые работы</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Услуги</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Услуги</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Демонтаж и черновые работы</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Выравнивание стен</t>
+        </is>
+      </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>mehanizirovannaya-shtukaturka</t>
+          <t>pereplanirovka-kvartiry</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3195,14 +3195,10 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Механизированная штукатурка</t>
-        </is>
-      </c>
+          <t>Перепланировка квартиры</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
@@ -3216,35 +3212,27 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>styazhka-pola</t>
+          <t>portfolio</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Стяжка пола</t>
-        </is>
-      </c>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
@@ -3258,35 +3246,27 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>demontazhnye-raboty</t>
+          <t>otzyvy</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Демонтажные работы</t>
-        </is>
-      </c>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
@@ -3300,35 +3280,27 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>vyravnivanie-sten</t>
+          <t>faq</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Демонтаж и черновые работы</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Выравнивание стен</t>
-        </is>
-      </c>
+          <t>Вопросы и ответы</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
@@ -3342,30 +3314,26 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>pereplanirovka-kvartiry</t>
+          <t>o-kompanii</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Главная</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Перепланировка квартиры</t>
-        </is>
-      </c>
+          <t>О компании</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
@@ -3380,13 +3348,13 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>portfolio</t>
+          <t>kontakty</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3396,7 +3364,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
@@ -3409,18 +3377,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>otzyvy</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
+          <t>partners</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>/partners</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3430,7 +3402,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
@@ -3448,13 +3420,13 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>faq</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3464,7 +3436,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
@@ -3482,13 +3454,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>o-kompanii</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
+          <t>politika-konfidencialnosti</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>/politicakonfident</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3498,7 +3474,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
@@ -3516,13 +3492,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>kontakty</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
+          <t>soglasie-na-obrabotku</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>/soglasienaobrabotku</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3532,7 +3512,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
@@ -3545,22 +3525,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Редирект</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>priyomka-kvartir-v-novostrojke</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>/partners</t>
+          <t>/priemka</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3570,7 +3550,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
@@ -3588,26 +3568,30 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>blog</t>
+          <t>priyomka-kvartiry-bez-otdelki</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартиры без отделки</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
@@ -3622,30 +3606,30 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>politika-konfidencialnosti</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>/politicakonfident</t>
-        </is>
-      </c>
+          <t>priyomka-kvartiry-s-otdelkoj</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr"/>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка квартиры с отделкой</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
@@ -3660,30 +3644,30 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>soglasie-na-obrabotku</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>/soglasienaobrabotku</t>
-        </is>
-      </c>
+          <t>priyomka-v-zhk-shablon</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Главная</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
+          <t>Приёмка квартир в новостройке</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Приёмка в ЖК (шаблон)</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
@@ -8096,555 +8080,555 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартир в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в новостройке в Москве | СК Эспада</t>
+          <t>Демонтаж и черновые работы в квартире в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры от застройщика с инженером: находим скрытые дефекты и составляем акт с замечаниями. Проверяем конструкции, отделку, окна и инженерные системы.</t>
+          <t>Черновой этап ремонта: демонтаж старой отделки и перегородок, стяжка пола, механизированная штукатурка, выравнивание стен. Сдаём этап с исполнительной документацией.</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в новостройке</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Механизированная штукатурка</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки в Москве | СК Эспада</t>
+          <t>Механизированная штукатурка стен в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки: проверяем геометрию стен, стяжку, окна, вентиляцию и вводы коммуникаций. Отдаём акт с замечаниями для передачи застройщику.</t>
+          <t>Механизированная штукатурка стен по маякам: ровная плоскость под чистовую отделку, скорость выше ручной в разы. Считаем по фактической площади, работаем по договору.</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры без отделки</t>
+          <t>Механизированная штукатурка стен</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Стяжка пола</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой от застройщика | СК Эспада</t>
+          <t>Стяжка пола в квартире в Москве, цена за м² | СК Эспада</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с чистовой отделкой: проверяем качество работ, сантехнику, электрику, двери и окна. Фиксируем дефекты в акте и помогаем добиться устранения.</t>
+          <t>Устройство стяжки пола, полусухой и мокрой, с гидроизоляцией мокрых зон. Выводим горизонт под ламинат и плитку. Считаем по площади, работаем по договору.</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Стяжка пола в квартире</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Демонтажные работы</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название} | СК Эспада</t>
+          <t>Демонтажные работы в квартире в Москве, цены | СК Эспада</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название}: знаем типовые дефекты этого дома и порядок работы с застройщиком. Выезд инженера с инструментом, акт в день осмотра.</t>
+          <t>Демонтаж в квартире: снос перегородок по согласованию, снятие старой отделки и стяжки, вывоз мусора. Работаем с допуском от управляющей компании.</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры в ЖК {Название}</t>
+          <t>Демонтажные работы в квартире</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Выравнивание стен</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы в квартире в Москве | СК Эспада</t>
+          <t>Выравнивание стен в квартире в Москве, цена | СК Эспада</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Черновой этап ремонта: демонтаж старой отделки и перегородок, стяжка пола, механизированная штукатурка, выравнивание стен. Сдаём этап с исполнительной документацией.</t>
+          <t>Выравнивание стен под чистовую отделку: штукатурка по маякам, шпатлёвка, контроль плоскости правилом. Считаем по фактической площади, смета в договоре.</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Выравнивание стен</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен в Москве, цена | СК Эспада</t>
+          <t>Перепланировка квартиры в Москве, согласование | СК Эспада</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен по маякам: ровная плоскость под чистовую отделку, скорость выше ручной в разы. Считаем по фактической площади, работаем по договору.</t>
+          <t>Перепланировка квартиры с согласованием: проект, техническое заключение, подача в жилищную инспекцию, ввод изменений в документы. Ведём весь процесс сами.</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Механизированная штукатурка стен</t>
+          <t>Перепланировка квартиры</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола в квартире в Москве, цена за м² | СК Эспада</t>
+          <t>Портфолио ремонтов квартир в Москве, фото работ | СК Эспада</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Устройство стяжки пола, полусухой и мокрой, с гидроизоляцией мокрых зон. Выводим горизонт под ламинат и плитку. Считаем по площади, работаем по договору.</t>
+          <t>Наши работы: фото готовых квартир, площадь, сроки и состав работ по каждому объекту. Фильтры по типу ремонта, числу комнат и жилому комплексу.</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Стяжка пола в квартире</t>
+          <t>Портфолио выполненных работ</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы в квартире в Москве, цены | СК Эспада</t>
+          <t>Отзывы о ремонте квартир от клиентов | СК Эспада</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж в квартире: снос перегородок по согласованию, снятие старой отделки и стяжки, вывоз мусора. Работаем с допуском от управляющей компании.</t>
+          <t>Отзывы клиентов о ремонте и дизайне квартир: что заказывали, как шли работы, что получилось. Каждый отзыв можно проверить, к нему приложены фото объекта.</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Демонтажные работы в квартире</t>
+          <t>Отзывы клиентов</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен в квартире в Москве, цена | СК Эспада</t>
+          <t>Вопросы и ответы о ремонте квартир | СК Эспада</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен под чистовую отделку: штукатурка по маякам, шпатлёвка, контроль плоскости правилом. Считаем по фактической площади, смета в договоре.</t>
+          <t>Отвечаем на вопросы о сроках, смете, договоре, оплате и гарантии. Что входит в ремонт под ключ, как считается стоимость и что делать при изменениях в проекте.</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Выравнивание стен</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры в Москве, согласование | СК Эспада</t>
+          <t>О компании СК Эспада, ремонт квартир в Москве</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры с согласованием: проект, техническое заключение, подача в жилищную инспекцию, ввод изменений в документы. Ведём весь процесс сами.</t>
+          <t>СК «Эспада» делает ремонт и дизайн квартир в Москве и области. Команда, гарантии, лицензии и реквизиты. Работаем по договору с фиксированной сметой.</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Перепланировка квартиры</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Портфолио ремонтов квартир в Москве, фото работ | СК Эспада</t>
+          <t>Контакты СК Эспада в Москве, адрес и телефон</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Наши работы: фото готовых квартир, площадь, сроки и состав работ по каждому объекту. Фильтры по типу ремонта, числу комнат и жилому комплексу.</t>
+          <t>Офис в Москве, улица Дегунинская, дом 1, корпус 2. Телефон +7 (993) 891-40-64, почта sk-espada@rambler.ru. Схема проезда и форма обратной связи.</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Портфолио выполненных работ</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Отзывы о ремонте квартир от клиентов | СК Эспада</t>
+          <t>Партнёрская программа для дизайнеров и агентов | СК Эспада</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Отзывы клиентов о ремонте и дизайне квартир: что заказывали, как шли работы, что получилось. Каждый отзыв можно проверить, к нему приложены фото объекта.</t>
+          <t>Партнёрам: стабильный поток клиентов, прозрачные условия и быстрые выплаты. Работаем с дизайнерами, риелторами и смежными подрядчиками. Оставьте заявку.</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Отзывы клиентов</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы о ремонте квартир | СК Эспада</t>
+          <t>Блог о ремонте и дизайне квартир | СК Эспада</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Отвечаем на вопросы о сроках, смете, договоре, оплате и гарантии. Что входит в ремонт под ключ, как считается стоимость и что делать при изменениях в проекте.</t>
+          <t>Статьи о ремонте и дизайне: как считать бюджет, что выбрать из материалов, с чего начинать работы и как контролировать подрядчика. Разборы от инженеров.</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Блог о ремонте и дизайне</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>О компании СК Эспада, ремонт квартир в Москве</t>
+          <t>Политика конфиденциальности | СК Эспада</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>СК «Эспада» делает ремонт и дизайн квартир в Москве и области. Команда, гарантии, лицензии и реквизиты. Работаем по договору с фиксированной сметой.</t>
+          <t>Как СК «Эспада» обрабатывает и защищает персональные данные посетителей сайта: какие данные собираются, для чего используются и как их удалить.</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Контакты СК Эспада в Москве, адрес и телефон</t>
+          <t>Согласие на обработку персональных данных | СК Эспада</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Офис в Москве, улица Дегунинская, дом 1, корпус 2. Телефон +7 (993) 891-40-64, почта sk-espada@rambler.ru. Схема проезда и форма обратной связи.</t>
+          <t>Текст согласия, которое посетитель даёт при отправке заявки на сайте: перечень данных, цели обработки, срок хранения и порядок отзыва согласия.</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Партнёрская программа для дизайнеров и агентов | СК Эспада</t>
+          <t>Приёмка квартиры в новостройке в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам: стабильный поток клиентов, прозрачные условия и быстрые выплаты. Работаем с дизайнерами, риелторами и смежными подрядчиками. Оставьте заявку.</t>
+          <t>Приёмка квартиры от застройщика с инженером: находим скрытые дефекты и составляем акт с замечаниями. Проверяем конструкции, отделку, окна и инженерные системы.</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Приёмка квартиры в новостройке</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Блог о ремонте и дизайне квартир | СК Эспада</t>
+          <t>Приёмка квартиры без отделки в Москве | СК Эспада</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Статьи о ремонте и дизайне: как считать бюджет, что выбрать из материалов, с чего начинать работы и как контролировать подрядчика. Разборы от инженеров.</t>
+          <t>Приёмка квартиры без отделки: проверяем геометрию стен, стяжку, окна, вентиляцию и вводы коммуникаций. Отдаём акт с замечаниями для передачи застройщику.</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Блог о ремонте и дизайне</t>
+          <t>Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности | СК Эспада</t>
+          <t>Приёмка квартиры с отделкой от застройщика | СК Эспада</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Как СК «Эспада» обрабатывает и защищает персональные данные посетителей сайта: какие данные собираются, для чего используются и как их удалить.</t>
+          <t>Приёмка квартиры с чистовой отделкой: проверяем качество работ, сантехнику, электрику, двери и окна. Фиксируем дефекты в акте и помогаем добиться устранения.</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
@@ -8654,32 +8638,32 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных | СК Эспада</t>
+          <t>Приёмка квартиры в ЖК {Название} | СК Эспада</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Текст согласия, которое посетитель даёт при отправке заявки на сайте: перечень данных, цели обработки, срок хранения и порядок отзыва согласия.</t>
+          <t>Приёмка квартиры в ЖК {Название}: знаем типовые дефекты этого дома и порядок работы с застройщиком. Выезд инженера с инструментом, акт в день осмотра.</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Приёмка квартиры в ЖК {Название}</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -12464,17 +12448,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+          <t>/demontazh-i-chernovye-raboty/</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Приёмка квартиры с отделкой</t>
+          <t>Демонтаж и черновые работы</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Приёмка</t>
+          <t>Услуги</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -12483,10 +12467,10 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>0</v>
@@ -12494,41 +12478,33 @@
       <c r="H72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>приемка квартиры пик с отделкой</t>
-        </is>
-      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Спроса нет</t>
+          <t>Спроса не найдено</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Записаться на приёмку</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>Посчитать ремонт после приёмки</t>
-        </is>
-      </c>
+          <t>Бесплатный расчёт сметы</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-v-zhk-shablon/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>Портфолио</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Приёмка</t>
+          <t>Доверие</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -12551,34 +12527,34 @@
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Поисковой роли нет</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Записаться на приёмку</t>
+          <t>Хочу такой же ремонт</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Посчитать ремонт после приёмки</t>
+          <t>Бесплатный расчёт сметы</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>/demontazh-i-chernovye-raboty/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Демонтаж и черновые работы</t>
+          <t>Отзывы</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Услуги</t>
+          <t>Доверие</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -12601,25 +12577,29 @@
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
+          <t>Поисковой роли нет</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
+          <t>Хочу такой же ремонт</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
           <t>Бесплатный расчёт сметы</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/faq/</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Вопросы и ответы</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -12664,12 +12644,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/o-kompanii/</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>О компании</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -12714,12 +12694,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>/faq/</t>
+          <t>/kontakty/</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Вопросы и ответы</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -12764,12 +12744,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>/o-kompanii/</t>
+          <t>/partners/</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>О компании</t>
+          <t>Партнёрам</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -12779,7 +12759,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Необходимо создать</t>
+          <t>Есть на сайте</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
@@ -12797,29 +12777,25 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Поисковой роли нет</t>
+          <t>Спроса не найдено</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Хочу такой же ремонт</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>Бесплатный расчёт сметы</t>
-        </is>
-      </c>
+          <t>Стать партнёром</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>/kontakty/</t>
+          <t>/blog/</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Блог</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -12864,22 +12840,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>/partners/</t>
+          <t>/politika-konfidencialnosti/</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Партнёрам</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Служебные</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Есть на сайте</t>
+          <t>Необходимо создать</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
@@ -12897,30 +12873,26 @@
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Спроса не найдено</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Стать партнёром</t>
-        </is>
-      </c>
+          <t>Поисковой роли нет</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/soglasie-na-obrabotku/</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Блог</t>
+          <t>Согласие на обработку персональных данных</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Доверие</t>
+          <t>Служебные</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -12946,31 +12918,23 @@
           <t>Поисковой роли нет</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Хочу такой же ремонт</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>Бесплатный расчёт сметы</t>
-        </is>
-      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>/politika-konfidencialnosti/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Служебные</t>
+          <t>Приёмка</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -12979,10 +12943,10 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>0</v>
@@ -12990,29 +12954,41 @@
       <c r="H82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>приемка квартиры пик с отделкой</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Поисковой роли нет</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
+          <t>Спроса нет</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Записаться на приёмку</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Посчитать ремонт после приёмки</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>/soglasie-na-obrabotku/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Согласие на обработку персональных данных</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Служебные</t>
+          <t>Приёмка</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -13035,11 +13011,19 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Поисковой роли нет</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
+          <t>Спроса не найдено</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Записаться на приёмку</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Посчитать ремонт после приёмки</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L83"/>
@@ -17293,11 +17277,11 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Приёмка квартир в новостройке</t>
+          <t>Приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -17305,11 +17289,7 @@
           <t>priyomka-kvartir-v-novostrojke</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>uslugi</t>
-        </is>
-      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>/priyomka-kvartir-v-novostrojke/</t>
@@ -17323,11 +17303,11 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Приёмка квартиры без отделки</t>
+          <t xml:space="preserve">    Приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -17353,11 +17333,11 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Приёмка квартиры с отделкой</t>
+          <t xml:space="preserve">    Приёмка квартиры с отделкой</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -17383,11 +17363,11 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Приёмка в ЖК (шаблон)</t>
+          <t xml:space="preserve">    Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -18283,7 +18263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E402"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -19848,17 +19828,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>приемка квартир москва в новостройках</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -19873,17 +19853,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>приемка квартир москва в новостройках</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -19898,17 +19878,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>приемка квартир москва в новостройках</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -19923,7 +19903,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -19948,7 +19928,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/remont-domov-i-kottedzhej/</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -19973,7 +19953,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -19998,7 +19978,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -20023,7 +20003,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -20048,7 +20028,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -20073,7 +20053,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -20098,7 +20078,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -20123,7 +20103,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -20148,7 +20128,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -20173,7 +20153,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -20198,7 +20178,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -20223,7 +20203,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -20248,7 +20228,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -20273,7 +20253,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -20298,7 +20278,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -20323,7 +20303,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -20348,7 +20328,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -20373,7 +20353,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -20398,7 +20378,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -20423,22 +20403,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>дизайн квартиры проект</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в кластер</t>
+          <t>Кластер в пиллар</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
@@ -20448,22 +20428,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект дома</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в кластер</t>
+          <t>Кластер в пиллар</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
@@ -20473,22 +20453,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект ванной комнаты</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в кластер</t>
+          <t>Кластер в пиллар</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
@@ -20503,12 +20483,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>арт дизайн кухни</t>
+          <t>дизайн квартиры проект</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -20528,12 +20508,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект офиса</t>
+          <t>дизайн проект дома</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -20553,12 +20533,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект спальни</t>
+          <t>дизайн проект ванной комнаты</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -20578,12 +20558,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект детской комнаты</t>
+          <t>арт дизайн кухни</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -20603,12 +20583,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект кафе</t>
+          <t>дизайн проект офиса</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -20623,17 +20603,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ремонт ванной комнаты</t>
+          <t>дизайн проект спальни</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -20648,17 +20628,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ремонт однокомнатной квартиры</t>
+          <t>дизайн проект детской комнаты</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -20673,17 +20653,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/dizajn-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>дизайн проект кафе</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -20698,17 +20678,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>приемка квартиры в новостройке без отделки</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -20723,17 +20703,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ремонт кухни</t>
+          <t>приемка квартиры пик с отделкой</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -20748,17 +20728,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -20778,12 +20758,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -20803,12 +20783,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -20828,12 +20808,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ремонт офиса</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -20853,12 +20833,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -20878,12 +20858,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>ремонт кухни</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -20903,12 +20883,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -20928,12 +20908,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -20953,12 +20933,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -20978,12 +20958,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>ремонт офиса</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -21003,12 +20983,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -21028,12 +21008,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -21053,12 +21033,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -21078,12 +21058,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -21103,12 +21083,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -21128,12 +21108,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -21153,12 +21133,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -21178,12 +21158,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -21203,12 +21183,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -21228,12 +21208,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -21253,12 +21233,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -21278,12 +21258,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -21303,12 +21283,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -21328,12 +21308,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>ремонт в 2х комнатной квартире панельного дома</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -21353,12 +21333,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>ремонт после пожара</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -21378,12 +21358,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартир и коттеджей</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -21398,167 +21378,167 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Между соседями</t>
+          <t>Пиллар в кластер</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Между соседями</t>
+          <t>Пиллар в кластер</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Между соседями</t>
+          <t>Пиллар в кластер</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Между соседями</t>
+          <t>Пиллар в кластер</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>ремонт после пожара</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Между соседями</t>
+          <t>Пиллар в кластер</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-domov-i-kottedzhej/</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт квартир и коттеджей</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Между соседями</t>
+          <t>Пиллар в кластер</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -21573,17 +21553,17 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>ремонт в 2х комнатной квартире панельного дома</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -21598,17 +21578,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>малярные работы</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -21623,17 +21603,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>укладка плитки цена за м2 в москве и московской</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -21648,17 +21628,17 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>сухая стяжка пола кнауф</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -21673,17 +21653,17 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>выравнивание стен по маякам</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -21698,17 +21678,17 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект офиса</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -21723,17 +21703,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект спальни</t>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -21748,17 +21728,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект кафе</t>
+          <t>малярные работы</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -21773,17 +21753,17 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>дизайн квартиры проект</t>
+          <t>укладка плитки цена за м2 в москве и московской</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -21798,17 +21778,17 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект ванной комнаты</t>
+          <t>сухая стяжка пола кнауф</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -21823,17 +21803,17 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>арт дизайн кухни</t>
+          <t>выравнивание стен по маякам</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -21848,17 +21828,17 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект дома</t>
+          <t>дизайн проект офиса</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -21873,17 +21853,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект ванной комнаты</t>
+          <t>дизайн проект спальни</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -21898,17 +21878,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект ванной комнаты</t>
+          <t>дизайн проект кафе</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -21923,17 +21903,17 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>арт дизайн кухни</t>
+          <t>дизайн квартиры проект</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -21948,17 +21928,17 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект спальни</t>
+          <t>дизайн проект ванной комнаты</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -21973,17 +21953,17 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект детской комнаты</t>
+          <t>арт дизайн кухни</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -21998,17 +21978,17 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+          <t>/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект спальни</t>
+          <t>дизайн проект дома</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -22023,17 +22003,17 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+          <t>/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект детской комнаты</t>
+          <t>дизайн проект ванной комнаты</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -22048,17 +22028,17 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект дома</t>
+          <t>дизайн проект ванной комнаты</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -22073,17 +22053,17 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>/dizajn-interera-ofisa/</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>/dizajn-kuhni/</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>/dizajn-vannoj-komnaty/</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект ванной комнаты</t>
+          <t>арт дизайн кухни</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -22098,17 +22078,17 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект офиса</t>
+          <t>дизайн проект спальни</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -22123,17 +22103,17 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект спальни</t>
+          <t>дизайн проект детской комнаты</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -22148,17 +22128,17 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>/dizajn-spalni/</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>/dizajn-kuhni/</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>арт дизайн кухни</t>
+          <t>дизайн проект спальни</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -22173,17 +22153,17 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-ofisa/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект офиса</t>
+          <t>дизайн проект детской комнаты</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -22198,17 +22178,17 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект детской комнаты</t>
+          <t>дизайн проект дома</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -22223,17 +22203,17 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kommercheskih-pomeshchenij/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект кафе</t>
+          <t>дизайн проект ванной комнаты</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -22248,17 +22228,17 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>дизайн квартиры проект</t>
+          <t>дизайн проект офиса</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -22273,17 +22253,17 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>дизайн проект дома</t>
+          <t>дизайн проект спальни</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -22298,7 +22278,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -22323,7 +22303,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -22348,17 +22328,17 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>дизайн проект детской комнаты</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -22373,17 +22353,17 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/dizajn-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>ремонт офиса</t>
+          <t>дизайн проект кафе</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -22398,17 +22378,17 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>дизайн квартиры проект</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -22423,17 +22403,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>дизайн проект дома</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -22448,17 +22428,17 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>замена радиаторов отопления</t>
+          <t>арт дизайн кухни</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -22473,17 +22453,17 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/dizajn-interera-ofisa/</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>для теплого пола подложка</t>
+          <t>дизайн проект офиса</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -22498,17 +22478,17 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>замена труб в ванной</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -22523,17 +22503,17 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>ремонт ванной комнаты</t>
+          <t>ремонт офиса</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -22548,17 +22528,17 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>ремонт однокомнатной квартиры</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -22573,17 +22553,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -22598,17 +22578,17 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>ремонт кухни</t>
+          <t>замена радиаторов отопления</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -22623,17 +22603,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -22648,17 +22628,17 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>ремонт кухни</t>
+          <t>замена труб в ванной</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -22673,17 +22653,17 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -22698,17 +22678,17 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -22723,17 +22703,17 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>приемка квартир москва в новостройках</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -22748,17 +22728,17 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>перепланировка квартиры в москве согласование</t>
+          <t>ремонт кухни</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -22773,17 +22753,17 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>комплектация дизайн проекта</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -22798,17 +22778,17 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>ремонт кухни</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -22823,17 +22803,17 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -22848,17 +22828,17 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -22873,17 +22853,17 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>перепланировка квартиры в москве согласование</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -22898,17 +22878,17 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
+          <t>/inzhenernye-sistemy/</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
           <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>/pereplanirovka-kvartiry/</t>
-        </is>
-      </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>перепланировка квартиры в москве согласование</t>
+          <t>комплектация дизайн проекта</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -22923,17 +22903,17 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>инженерные системы</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -22948,17 +22928,17 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -22973,17 +22953,17 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -22998,17 +22978,17 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -23023,17 +23003,17 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>перепланировка квартиры в москве согласование</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -23048,17 +23028,17 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>декоративная штукатурка</t>
+          <t>инженерные системы</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -23073,17 +23053,17 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>укладка плитки цена за м2 в москве и московской</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -23098,17 +23078,17 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>материалы натяжных потолков</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -23123,17 +23103,17 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>сухая стяжка пола кнауф</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -23148,17 +23128,17 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>выравнивание стен по маякам</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -23173,17 +23153,17 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>малярные работы</t>
+          <t>декоративная штукатурка</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -23198,7 +23178,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -23223,17 +23203,17 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>материалы натяжных потолков</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -23248,17 +23228,17 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>сухая стяжка пола кнауф</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -23273,17 +23253,17 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>выравнивание стен по маякам</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -23298,17 +23278,17 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>малярные работы</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -23323,17 +23303,17 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>вентиляция в квартире</t>
+          <t>укладка плитки цена за м2 в москве и московской</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -23348,17 +23328,17 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -23373,17 +23353,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>для теплого пола подложка</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -23398,17 +23378,17 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>электромонтаж в квартире</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -23423,17 +23403,17 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>приемка квартир москва в новостройках</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -23448,17 +23428,17 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>инженерные системы</t>
+          <t>вентиляция в квартире</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -23473,17 +23453,17 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>комплектация дизайн проекта</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -23498,17 +23478,17 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>перепланировка квартиры в москве согласование</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -23523,17 +23503,17 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>инженерные системы</t>
+          <t>электромонтаж в квартире</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -23548,17 +23528,17 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>приемка квартиры пик с отделкой</t>
+          <t>инженерные системы</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -23573,17 +23553,17 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-v-zhk-shablon/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Приёмка в ЖК (шаблон)</t>
+          <t>комплектация дизайн проекта</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -23598,17 +23578,17 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
           <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
-        </is>
-      </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>приемка квартиры в новостройке без отделки</t>
+          <t>приемка квартиры пик с отделкой</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -23623,7 +23603,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -23648,7 +23628,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-v-zhk-shablon/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -23673,17 +23653,17 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
           <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>/priyomka-kvartiry-s-otdelkoj/</t>
-        </is>
-      </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>приемка квартиры пик с отделкой</t>
+          <t>Приёмка в ЖК (шаблон)</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -23698,17 +23678,17 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>ремонт однокомнатной квартиры</t>
+          <t>приемка квартиры в новостройке без отделки</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -23723,17 +23703,17 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/priyomka-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/priyomka-kvartiry-s-otdelkoj/</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>приемка квартиры пик с отделкой</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -23753,12 +23733,12 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>ремонт кухни</t>
+          <t>ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -23778,12 +23758,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -23798,17 +23778,17 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>ремонт в 2х комнатной квартире панельного дома</t>
+          <t>ремонт кухни</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -23823,17 +23803,17 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>ремонт после пожара</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -23848,17 +23828,17 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-domov-i-kottedzhej/</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -23873,17 +23853,17 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-domov-i-kottedzhej/</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>ремонт после пожара</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -23903,12 +23883,12 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -23928,12 +23908,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -23948,17 +23928,17 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -23973,17 +23953,17 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -24003,12 +23983,12 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>ремонт в 2х комнатной квартире панельного дома</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -24028,12 +24008,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>ремонт после пожара</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -24048,17 +24028,17 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -24073,17 +24053,17 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>ремонт после пожара</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -24103,12 +24083,12 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -24128,12 +24108,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>ремонт в жк titul</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -24148,17 +24128,17 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -24173,17 +24153,17 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>ремонт в жк titul</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -24203,12 +24183,12 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -24228,12 +24208,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -24248,17 +24228,17 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -24273,17 +24253,17 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>ремонт туалета</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -24303,12 +24283,12 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -24328,12 +24308,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт туалета</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -24348,17 +24328,17 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -24373,17 +24353,17 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -24403,12 +24383,12 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -24428,12 +24408,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -24448,17 +24428,17 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -24473,17 +24453,17 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -24503,12 +24483,12 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -24528,12 +24508,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -24548,17 +24528,17 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -24573,17 +24553,17 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>ремонт санузла под ключ</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -24603,12 +24583,12 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>ремонт офиса</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -24628,12 +24608,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>ремонт санузла под ключ</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -24648,17 +24628,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>ремонт ванной комнаты</t>
+          <t>ремонт офиса</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -24673,17 +24653,17 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -24703,12 +24683,12 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>/remont-balkona-i-lodzhii/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>ремонт балкона</t>
+          <t>ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -24723,17 +24703,17 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -24748,17 +24728,17 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-balkona-i-lodzhii/</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>ремонт балкона</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -24778,12 +24758,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -24803,12 +24783,12 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -24823,17 +24803,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -24848,17 +24828,17 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>ремонт в 2х комнатной квартире панельного дома</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -24878,12 +24858,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартир и коттеджей</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -24898,17 +24878,17 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>ремонт в 2х комнатной квартире панельного дома</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -24923,17 +24903,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/remont-domov-i-kottedzhej/</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>ремонт 2 комнатной квартиры</t>
+          <t>ремонт квартир и коттеджей</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -24953,12 +24933,12 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -24978,12 +24958,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>ремонт 2 комнатной квартиры</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -24998,17 +24978,17 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>ремонт кухни</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -25023,17 +25003,17 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>евроремонт</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -25053,12 +25033,12 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
+          <t>ремонт кухни</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -25078,12 +25058,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>ремонт офиса</t>
+          <t>евроремонт</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -25098,17 +25078,17 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>сколько стоит сделать ремонт в новостройке с нуля</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -25123,17 +25103,17 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>ремонт офиса</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -25153,12 +25133,12 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-studii/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>ремонт студии под ключ</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -25178,12 +25158,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -25198,17 +25178,17 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-kvartiry-studii/</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>ремонт в хрущевке</t>
+          <t>ремонт студии под ключ</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -25223,17 +25203,17 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -25253,12 +25233,12 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>ремонт в сталинке</t>
+          <t>ремонт в хрущевке</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -25278,12 +25258,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -25298,17 +25278,17 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>ремонт в сталинке</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -25323,17 +25303,17 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -25353,12 +25333,12 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>ремонт в стиле лофт</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -25378,12 +25358,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>ремонт капитальный квартиры</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -25398,17 +25378,17 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>ремонт коридора</t>
+          <t>ремонт в стиле лофт</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -25423,17 +25403,17 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
+          <t>ремонт капитальный квартиры</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -25453,12 +25433,12 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>ремонт коридора</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -25478,12 +25458,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>сколько стоит ремонт квартиры в москве под ключ за м2 вторичка</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -25498,17 +25478,17 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>чистовой ремонт квартиры</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -25523,17 +25503,17 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>ремонт гостиной</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -25553,12 +25533,12 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>/remont-posle-zaliva-i-pozhara/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>ремонт после пожара</t>
+          <t>чистовой ремонт квартиры</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -25578,12 +25558,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>/remont-domov-i-kottedzhej/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартир и коттеджей</t>
+          <t>ремонт гостиной</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -25598,17 +25578,17 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/remont-posle-zaliva-i-pozhara/</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>черновой ремонт квартир</t>
+          <t>ремонт после пожара</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -25623,17 +25603,17 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-stalinke/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-domov-i-kottedzhej/</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>ремонт трехкомнатной квартиры под ключ</t>
+          <t>ремонт квартир и коттеджей</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -25653,12 +25633,12 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>ремонт квартиры под сдачу</t>
+          <t>черновой ремонт квартир</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -25678,12 +25658,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>ремонт в спальне</t>
+          <t>ремонт трехкомнатной квартиры под ключ</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -25698,17 +25678,17 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>/remont-kommercheskih-pomeshchenij/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>ремонт офиса</t>
+          <t>ремонт квартиры под сдачу</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -25723,17 +25703,17 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-zhk-shablon/</t>
+          <t>/remont-v-stalinke/</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>ремонт по дизайн проекту</t>
+          <t>ремонт в спальне</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -25753,12 +25733,12 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/remont-kommercheskih-pomeshchenij/</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>косметический ремонт квартир в москве</t>
+          <t>ремонт офиса</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -25778,12 +25758,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>сделать ремонт в квартире недорого</t>
+          <t>ремонт по дизайн проекту</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -25798,17 +25778,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>ремонт однокомнатной квартиры</t>
+          <t>косметический ремонт квартир в москве</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -25823,17 +25803,17 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-v-zhk-shablon/</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>/elitnyj-remont-kvartir/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>элитная отделка квартир</t>
+          <t>сделать ремонт в квартире недорого</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
@@ -25848,17 +25828,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>для теплого пола подложка</t>
+          <t>ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
@@ -25873,17 +25853,17 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/elitnyj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>электромонтаж в квартире</t>
+          <t>элитная отделка квартир</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -25898,17 +25878,17 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>установка кондиционера</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -25923,17 +25903,17 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>вентиляция в квартире</t>
+          <t>электромонтаж в квартире</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -25953,12 +25933,12 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>замена радиаторов отопления</t>
+          <t>установка кондиционера</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -25978,12 +25958,12 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>для теплого пола подложка</t>
+          <t>вентиляция в квартире</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -25998,17 +25978,17 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>штукатурка механизированная</t>
+          <t>замена радиаторов отопления</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
@@ -26023,17 +26003,17 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>выравнивание стен по маякам</t>
+          <t>для теплого пола подложка</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
@@ -26053,12 +26033,12 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>демонтажные работы</t>
+          <t>штукатурка механизированная</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
@@ -26073,17 +26053,17 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>выравнивание стен по маякам</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -26098,17 +26078,17 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>замена радиаторов отопления</t>
+          <t>демонтажные работы</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -26128,12 +26108,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>электромонтаж в квартире</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -26153,12 +26133,12 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>замена труб в ванной</t>
+          <t>замена радиаторов отопления</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
@@ -26173,17 +26153,17 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>декоративная штукатурка</t>
+          <t>электромонтаж в квартире</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -26198,17 +26178,17 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>малярные работы</t>
+          <t>замена труб в ванной</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
@@ -26228,12 +26208,12 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>материалы натяжных потолков</t>
+          <t>декоративная штукатурка</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -26248,17 +26228,17 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>установка кондиционера</t>
+          <t>малярные работы</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -26273,17 +26253,17 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>вентиляция в квартире</t>
+          <t>материалы натяжных потолков</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -26298,17 +26278,17 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
+          <t>/umnyj-dom/</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
           <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
-      <c r="B321" s="2" t="inlineStr">
-        <is>
-          <t>/umnyj-dom/</t>
-        </is>
-      </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>умный дом</t>
+          <t>установка кондиционера</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -26323,7 +26303,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -26353,12 +26333,12 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>умный дом</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
@@ -26373,17 +26353,17 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
+          <t>/ustanovka-konditsionerov/</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
           <t>/ventilyatsiya/</t>
         </is>
       </c>
-      <c r="B324" s="2" t="inlineStr">
-        <is>
-          <t>/umnyj-dom/</t>
-        </is>
-      </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>умный дом</t>
+          <t>вентиляция в квартире</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
@@ -26398,17 +26378,17 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>установка кондиционера</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -26428,12 +26408,12 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>шумоизоляция двери входной</t>
+          <t>умный дом</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
@@ -26453,12 +26433,12 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>замена радиаторов отопления</t>
+          <t>установка кондиционера</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
@@ -26473,17 +26453,17 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>штукатурка механизированная</t>
+          <t>шумоизоляция двери входной</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
@@ -26498,17 +26478,17 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>сухая стяжка пола кнауф</t>
+          <t>замена радиаторов отопления</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
@@ -26528,12 +26508,12 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>/demontazhnye-raboty/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>демонтажные работы</t>
+          <t>штукатурка механизированная</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
@@ -26548,22 +26528,22 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>сухая стяжка пола кнауф</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Услуга в пиллар</t>
+          <t>Между соседями</t>
         </is>
       </c>
       <c r="E331" s="2" t="n">
@@ -26573,22 +26553,22 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
+          <t>/vyravnivanie-sten/</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
           <t>/demontazhnye-raboty/</t>
         </is>
       </c>
-      <c r="B332" s="2" t="inlineStr">
-        <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
-        </is>
-      </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>ремонт и отделка</t>
+          <t>демонтажные работы</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Услуга в пиллар</t>
+          <t>Между соседями</t>
         </is>
       </c>
       <c r="E332" s="2" t="n">
@@ -26598,7 +26578,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -26623,7 +26603,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>/inzhenernye-sistemy/</t>
+          <t>/demontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -26648,7 +26628,7 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -26673,7 +26653,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/inzhenernye-sistemy/</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -26698,7 +26678,7 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>/mehanizirovannaya-shtukaturka/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -26723,7 +26703,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -26748,7 +26728,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/mehanizirovannaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -26773,7 +26753,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -26798,7 +26778,7 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -26823,7 +26803,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -26848,7 +26828,7 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -26873,7 +26853,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -26898,7 +26878,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -26923,7 +26903,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>/umnyj-dom/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -26948,7 +26928,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>/ustanovka-konditsionerov/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -26973,7 +26953,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>/ventilyatsiya/</t>
+          <t>/umnyj-dom/</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -26998,7 +26978,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/ustanovka-konditsionerov/</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -27023,7 +27003,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/ventilyatsiya/</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -27038,42 +27018,42 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Доверие в пиллар</t>
+          <t>Услуга в пиллар</t>
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>дизайн интерьера</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Доверие в пиллар</t>
+          <t>Услуга в пиллар</t>
         </is>
       </c>
       <c r="E351" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -27098,7 +27078,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -27123,22 +27103,22 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>/chernovoj-remont-kvartiry/</t>
+          <t>/otzyvy/</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>/blog/chernovoj-remont-kvartiry/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, черновой ремонт квартиры</t>
+          <t>приемка квартир москва в новостройках</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Коммерция в блог</t>
+          <t>Доверие в пиллар</t>
         </is>
       </c>
       <c r="E354" s="2" t="n">
@@ -27148,22 +27128,22 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>/chistovaya-otdelka-kvartiry/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/blog/chistovaya-otdelka-kvartiry/</t>
+          <t>/remont-kvartir-pod-klyuch/</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, чистовая отделка квартиры</t>
+          <t>ремонт и отделка</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Коммерция в блог</t>
+          <t>Доверие в пиллар</t>
         </is>
       </c>
       <c r="E355" s="2" t="n">
@@ -27173,22 +27153,22 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>/dekorativnaya-shtukaturka/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/blog/dekorativnaya-shtukaturka/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, декоративная штукатурка</t>
+          <t>дизайн интерьера</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Коммерция в блог</t>
+          <t>Доверие в пиллар</t>
         </is>
       </c>
       <c r="E356" s="2" t="n">
@@ -27198,22 +27178,22 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-detskoj-komnaty/</t>
+          <t>/portfolio/</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-detskoj-komnaty/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн детской комнаты</t>
+          <t>приемка квартир москва в новостройках</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Коммерция в блог</t>
+          <t>Доверие в пиллар</t>
         </is>
       </c>
       <c r="E357" s="2" t="n">
@@ -27223,17 +27203,17 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-doma/</t>
+          <t>/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-interera-doma/</t>
+          <t>/blog/chernovoj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн интерьера дома</t>
+          <t>Статьи о том, черновой ремонт квартиры</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -27248,17 +27228,17 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera-kvartiry/</t>
+          <t>/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-interera-kvartiry/</t>
+          <t>/blog/chistovaya-otdelka-kvartiry/</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн интерьера квартиры</t>
+          <t>Статьи о том, чистовая отделка квартиры</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -27273,17 +27253,17 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-interera/</t>
+          <t>/blog/dekorativnaya-shtukaturka/</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн интерьера</t>
+          <t>Статьи о том, декоративная штукатурка</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -27298,17 +27278,17 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-kuhni/</t>
+          <t>/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-kuhni/</t>
+          <t>/blog/dizajn-detskoj-komnaty/</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн кухни</t>
+          <t>Статьи о том, дизайн детской комнаты</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -27323,17 +27303,17 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-spalni/</t>
+          <t>/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-spalni/</t>
+          <t>/blog/dizajn-interera-doma/</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн спальни</t>
+          <t>Статьи о том, дизайн интерьера дома</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -27348,17 +27328,17 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-vannoj-komnaty/</t>
+          <t>/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajn-vannoj-komnaty/</t>
+          <t>/blog/dizajn-interera-kvartiry/</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайн ванной комнаты</t>
+          <t>Статьи о том, дизайн интерьера квартиры</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -27373,17 +27353,17 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>/dizajnerskij-remont-kvartiry/</t>
+          <t>/dizajn-interera/</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>/blog/dizajnerskij-remont-kvartiry/</t>
+          <t>/blog/dizajn-interera/</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, дизайнерский ремонт квартиры</t>
+          <t>Статьи о том, дизайн интерьера</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -27398,17 +27378,17 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>/elektromontazhnye-raboty/</t>
+          <t>/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/blog/elektromontazhnye-raboty/</t>
+          <t>/blog/dizajn-kuhni/</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, электромонтажные работы</t>
+          <t>Статьи о том, дизайн кухни</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -27423,17 +27403,17 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>/evroremont-kvartiry/</t>
+          <t>/dizajn-spalni/</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>/blog/evroremont-kvartiry/</t>
+          <t>/blog/dizajn-spalni/</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, евроремонт квартиры</t>
+          <t>Статьи о том, дизайн спальни</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -27448,17 +27428,17 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>/kapitalnyj-remont-kvartiry/</t>
+          <t>/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>/blog/kapitalnyj-remont-kvartiry/</t>
+          <t>/blog/dizajn-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, капитальный ремонт квартиры</t>
+          <t>Статьи о том, дизайн ванной комнаты</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -27473,17 +27453,17 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>/komplektatsiya-kvartiry/</t>
+          <t>/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/blog/komplektatsiya-kvartiry/</t>
+          <t>/blog/dizajnerskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, комплектация квартиры</t>
+          <t>Статьи о том, дизайнерский ремонт квартиры</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -27498,17 +27478,17 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>/kosmeticheskij-remont-kvartiry/</t>
+          <t>/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/blog/kosmeticheskij-remont-kvartiry/</t>
+          <t>/blog/elektromontazhnye-raboty/</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, косметический ремонт квартиры</t>
+          <t>Статьи о том, электромонтажные работы</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
@@ -27523,17 +27503,17 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>/blog/malyarnye-raboty-i-poklejka-oboev/</t>
+          <t>/blog/evroremont-kvartiry/</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, малярные работы и поклейка обоев</t>
+          <t>Статьи о том, евроремонт квартиры</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -27548,17 +27528,17 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>/natyazhnye-potolki/</t>
+          <t>/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>/blog/natyazhnye-potolki/</t>
+          <t>/blog/kapitalnyj-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, натяжные потолки</t>
+          <t>Статьи о том, капитальный ремонт квартиры</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -27573,17 +27553,17 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>/nedorogoj-remont-kvartir/</t>
+          <t>/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/blog/nedorogoj-remont-kvartir/</t>
+          <t>/blog/komplektatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, недорогой ремонт квартир</t>
+          <t>Статьи о том, комплектация квартиры</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -27598,17 +27578,17 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>/otoplenie-i-radiatory/</t>
+          <t>/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/blog/otoplenie-i-radiatory/</t>
+          <t>/blog/kosmeticheskij-remont-kvartiry/</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, отопление и радиаторы</t>
+          <t>Статьи о том, косметический ремонт квартиры</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -27623,17 +27603,17 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>/pereplanirovka-kvartiry/</t>
+          <t>/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>/blog/pereplanirovka-kvartiry/</t>
+          <t>/blog/malyarnye-raboty-i-poklejka-oboev/</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, перепланировка квартиры</t>
+          <t>Статьи о том, малярные работы и поклейка обоев</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -27648,17 +27628,17 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartir-v-novostrojke/</t>
+          <t>/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>/blog/priyomka-kvartir-v-novostrojke/</t>
+          <t>/blog/natyazhnye-potolki/</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, приёмка квартир в новостройке</t>
+          <t>Статьи о том, натяжные потолки</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -27673,17 +27653,17 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/blog/priyomka-kvartiry-bez-otdelki/</t>
+          <t>/blog/nedorogoj-remont-kvartir/</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, приёмка квартиры без отделки</t>
+          <t>Статьи о том, недорогой ремонт квартир</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
@@ -27698,17 +27678,17 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-dvuhkomnatnoj-kvartiry/</t>
+          <t>/blog/otoplenie-i-radiatory/</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт двухкомнатной квартиры</t>
+          <t>Статьи о том, отопление и радиаторы</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
@@ -27723,17 +27703,17 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>/remont-gostinoj/</t>
+          <t>/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-gostinoj/</t>
+          <t>/blog/pereplanirovka-kvartiry/</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт гостиной</t>
+          <t>Статьи о том, перепланировка квартиры</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
@@ -27748,17 +27728,17 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>/remont-kuhni/</t>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kuhni/</t>
+          <t>/blog/priyomka-kvartir-v-novostrojke/</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт кухни</t>
+          <t>Статьи о том, приёмка квартир в новостройке</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
@@ -27773,17 +27753,17 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-po-stilyu/</t>
+          <t>/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kvartir-po-stilyu/</t>
+          <t>/blog/priyomka-kvartiry-bez-otdelki/</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт квартир по стилю</t>
+          <t>Статьи о том, приёмка квартиры без отделки</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
@@ -27798,17 +27778,17 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-na-vtorichke/</t>
+          <t>/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kvartiry-na-vtorichke/</t>
+          <t>/blog/remont-dvuhkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт квартиры на вторичке</t>
+          <t>Статьи о том, ремонт двухкомнатной квартиры</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
@@ -27823,17 +27803,17 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartiry-v-novostrojke/</t>
+          <t>/remont-gostinoj/</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-kvartiry-v-novostrojke/</t>
+          <t>/blog/remont-gostinoj/</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт квартиры в новостройке</t>
+          <t>Статьи о том, ремонт гостиной</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
@@ -27848,17 +27828,17 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/remont-kuhni/</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-odnokomnatnoj-kvartiry/</t>
+          <t>/blog/remont-kuhni/</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт однокомнатной квартиры</t>
+          <t>Статьи о том, ремонт кухни</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
@@ -27873,17 +27853,17 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>/remont-pod-sdachu-v-arendu/</t>
+          <t>/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-pod-sdachu-v-arendu/</t>
+          <t>/blog/remont-kvartir-po-stilyu/</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт под сдачу в аренду</t>
+          <t>Статьи о том, ремонт квартир по стилю</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -27898,17 +27878,17 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>/remont-prihozhej-i-koridora/</t>
+          <t>/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-prihozhej-i-koridora/</t>
+          <t>/blog/remont-kvartiry-na-vtorichke/</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт прихожей и коридора</t>
+          <t>Статьи о том, ремонт квартиры на вторичке</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -27923,17 +27903,17 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>/remont-sanuzla/</t>
+          <t>/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-sanuzla/</t>
+          <t>/blog/remont-kvartiry-v-novostrojke/</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт санузла</t>
+          <t>Статьи о том, ремонт квартиры в новостройке</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -27948,17 +27928,17 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>/remont-spalni/</t>
+          <t>/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-spalni/</t>
+          <t>/blog/remont-odnokomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт спальни</t>
+          <t>Статьи о том, ремонт однокомнатной квартиры</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -27973,17 +27953,17 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-tryohkomnatnoj-kvartiry/</t>
+          <t>/blog/remont-pod-sdachu-v-arendu/</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт трёхкомнатной квартиры</t>
+          <t>Статьи о том, ремонт под сдачу в аренду</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -27998,17 +27978,17 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>/remont-tualeta/</t>
+          <t>/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-tualeta/</t>
+          <t>/blog/remont-prihozhej-i-koridora/</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт туалета</t>
+          <t>Статьи о том, ремонт прихожей и коридора</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
@@ -28023,17 +28003,17 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-hrushchyovke/</t>
+          <t>/remont-sanuzla/</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-v-hrushchyovke/</t>
+          <t>/blog/remont-sanuzla/</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт в хрущёвке</t>
+          <t>Статьи о том, ремонт санузла</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -28048,17 +28028,17 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>/remont-v-panelnom-dome/</t>
+          <t>/remont-spalni/</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-v-panelnom-dome/</t>
+          <t>/blog/remont-spalni/</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт в панельном доме</t>
+          <t>Статьи о том, ремонт спальни</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
@@ -28073,17 +28053,17 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>/remont-vannoj-komnaty/</t>
+          <t>/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>/blog/remont-vannoj-komnaty/</t>
+          <t>/blog/remont-tryohkomnatnoj-kvartiry/</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, ремонт ванной комнаты</t>
+          <t>Статьи о том, ремонт трёхкомнатной квартиры</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -28098,17 +28078,17 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>/santehnicheskie-raboty/</t>
+          <t>/remont-tualeta/</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>/blog/santehnicheskie-raboty/</t>
+          <t>/blog/remont-tualeta/</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, сантехнические работы</t>
+          <t>Статьи о том, ремонт туалета</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
@@ -28123,17 +28103,17 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>/shumoizolyatsiya-kvartiry/</t>
+          <t>/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>/blog/shumoizolyatsiya-kvartiry/</t>
+          <t>/blog/remont-v-hrushchyovke/</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, шумоизоляция квартиры</t>
+          <t>Статьи о том, ремонт в хрущёвке</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -28148,17 +28128,17 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>/styazhka-pola/</t>
+          <t>/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>/blog/styazhka-pola/</t>
+          <t>/blog/remont-v-panelnom-dome/</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, стяжка пола</t>
+          <t>Статьи о том, ремонт в панельном доме</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
@@ -28173,17 +28153,17 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>/tyoplyj-pol/</t>
+          <t>/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>/blog/tyoplyj-pol/</t>
+          <t>/blog/remont-vannoj-komnaty/</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, тёплый пол</t>
+          <t>Статьи о том, ремонт ванной комнаты</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -28198,17 +28178,17 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>/ukladka-plitki/</t>
+          <t>/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>/blog/ukladka-plitki/</t>
+          <t>/blog/santehnicheskie-raboty/</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, укладка плитки</t>
+          <t>Статьи о том, сантехнические работы</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -28223,17 +28203,17 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>/vyravnivanie-sten/</t>
+          <t>/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>/blog/vyravnivanie-sten/</t>
+          <t>/blog/shumoizolyatsiya-kvartiry/</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Статьи о том, выравнивание стен</t>
+          <t>Статьи о том, шумоизоляция квартиры</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
@@ -28248,22 +28228,22 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/styazhka-pola/</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/blog/styazhka-pola/</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Статьи о том, стяжка пола</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в доверие</t>
+          <t>Коммерция в блог</t>
         </is>
       </c>
       <c r="E399" s="2" t="n">
@@ -28273,22 +28253,22 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>/dizajn-interera/</t>
+          <t>/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/blog/tyoplyj-pol/</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Статьи о том, тёплый пол</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в доверие</t>
+          <t>Коммерция в блог</t>
         </is>
       </c>
       <c r="E400" s="2" t="n">
@@ -28298,22 +28278,22 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/ukladka-plitki/</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/portfolio/</t>
+          <t>/blog/ukladka-plitki/</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>Портфолио</t>
+          <t>Статьи о том, укладка плитки</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в доверие</t>
+          <t>Коммерция в блог</t>
         </is>
       </c>
       <c r="E401" s="2" t="n">
@@ -28323,30 +28303,180 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>/remont-kvartir-pod-klyuch/</t>
+          <t>/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/otzyvy/</t>
+          <t>/blog/vyravnivanie-sten/</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Отзывы</t>
+          <t>Статьи о том, выравнивание стен</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Пиллар в доверие</t>
+          <t>Коммерция в блог</t>
         </is>
       </c>
       <c r="E402" s="2" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-interera/</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>/dizajn-interera/</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>/priyomka-kvartir-v-novostrojke/</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kvartir-pod-klyuch/</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>/portfolio/</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>Портфолио</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>/remont-kvartir-pod-klyuch/</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>/otzyvy/</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>Отзывы</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Пиллар в доверие</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E402"/>
+  <autoFilter ref="A1:E408"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>